--- a/data/Indoor plants.xlsx
+++ b/data/Indoor plants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E51904-FA6D-459D-B4DE-8583A33F7B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E83758E-A7B6-4B44-84EE-48B7F6BE4D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -75,9 +75,6 @@
     <t>Hibiscus rosa-sinensis</t>
   </si>
   <si>
-    <t>Chinese hibiscus</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/LnN3pB41/Chinese-Hibiscus.jpg</t>
   </si>
   <si>
@@ -99,9 +96,6 @@
     <t>Philodendron hederaceum</t>
   </si>
   <si>
-    <t>Heartleaf Philodendron</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/nMnmhjPY/heartleaf.jpg</t>
   </si>
   <si>
@@ -117,9 +111,6 @@
     <t>Euphorbia milii</t>
   </si>
   <si>
-    <t>Crown of Thorns</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/sQY50501/crown-of-thorns.jpg</t>
   </si>
   <si>
@@ -135,9 +126,6 @@
     <t>Syngonium podophyllum</t>
   </si>
   <si>
-    <t>Arrowhead Plant</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/hQMDYY0h/Arrowhead.jpg</t>
   </si>
   <si>
@@ -150,9 +138,6 @@
     <t>Epipremnum aureum</t>
   </si>
   <si>
-    <t>Golden Pothos, Devil’s Ivy</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/KkDg5xRM/golden-phothos.jpg</t>
   </si>
   <si>
@@ -168,9 +153,6 @@
     <t>Scindapsus pictus</t>
   </si>
   <si>
-    <t>Satin pothos</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/TyZpjBk6/Satin-pothos.jpg</t>
   </si>
   <si>
@@ -186,9 +168,6 @@
     <t>Araucaria heterophylla</t>
   </si>
   <si>
-    <t>Norfolk Island Pine, Indoor Christmas Tree</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/Pvdf2HYB/Araucaria-heterophylla-Norfolk-Island-pine.jpg</t>
   </si>
   <si>
@@ -204,9 +183,6 @@
     <t>Ravenea rivularis</t>
   </si>
   <si>
-    <t>Majestic Palm</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/TKdmp8sN/Majestic-Palm.jpg</t>
   </si>
   <si>
@@ -219,9 +195,6 @@
     <t>Schefflera arboricola</t>
   </si>
   <si>
-    <t>Dwarf Umbrella Tree</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/fJ2mFz57/Dwarf-Umbrella-Tree.jpg</t>
   </si>
   <si>
@@ -234,9 +207,6 @@
     <t>Dracaena marginata</t>
   </si>
   <si>
-    <t>Madagascar Dragon Tree</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/mzvCDPx7/Madagascar-dragon-tree.jpg</t>
   </si>
   <si>
@@ -252,9 +222,6 @@
     <t>Dracaena angustifolia</t>
   </si>
   <si>
-    <t>Rainbow tree</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/3kfyNkmW/Rainbow-tree.jpg</t>
   </si>
   <si>
@@ -270,9 +237,6 @@
     <t>Sansevieria cylindrica</t>
   </si>
   <si>
-    <t>Cylindrical Snake Plant</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/Yj76LyhF/cylindrical-snake-plant.jpg</t>
   </si>
   <si>
@@ -285,9 +249,6 @@
     <t>Pachira glabra</t>
   </si>
   <si>
-    <t>Money Tree</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/67SGj8pF/Money-tree.jpg</t>
   </si>
   <si>
@@ -303,9 +264,6 @@
     <t>Ficus elastica</t>
   </si>
   <si>
-    <t>Rubber Plant</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/NyyKHQkD/Rubber-tree-Ficus-elastica.jpg</t>
   </si>
   <si>
@@ -321,9 +279,6 @@
     <t>Codiaeum variegatum</t>
   </si>
   <si>
-    <t>Garden Croton</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/fVyjTtkg/Codiaeum-variegatum-Garden-croton.jpg</t>
   </si>
   <si>
@@ -336,9 +291,6 @@
     <t>Ficus microcapa</t>
   </si>
   <si>
-    <t>Indian Laurel</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/rDDx2BYB/Ficus-microcarpa.jpg</t>
   </si>
   <si>
@@ -351,9 +303,6 @@
     <t>Kalanchoe blossfeldiana</t>
   </si>
   <si>
-    <t>Florist kalanchoe</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/LgjfZmRw/Kalanchoe-blossfeldiana.jpg</t>
   </si>
   <si>
@@ -369,9 +318,6 @@
     <t>Bougainvillea glabra</t>
   </si>
   <si>
-    <t>Paper Flower</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/1nqVLygX/Paper-flower.jpg</t>
   </si>
   <si>
@@ -387,9 +333,6 @@
     <t>Dracaena fragrans</t>
   </si>
   <si>
-    <t>Corn Plant</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/yg4FPLjw/Corn-Plant.jpg</t>
   </si>
   <si>
@@ -402,9 +345,6 @@
     <t>Zamioculcas zamiifolia</t>
   </si>
   <si>
-    <t>Zanzibar Gem</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/476N6y76/Zanzibar-Gem-2.jpg</t>
   </si>
   <si>
@@ -421,9 +361,6 @@
   </si>
   <si>
     <t xml:space="preserve">Lavandula angustifolia </t>
-  </si>
-  <si>
-    <t>English Lavender</t>
   </si>
   <si>
     <t>https://i.postimg.cc/75j7HKFf/English-lavender.jpg</t>
@@ -450,9 +387,6 @@
     </r>
   </si>
   <si>
-    <t>Lemon Grass</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/WhP0cqwv/LEMON-GRASS.jpg</t>
   </si>
   <si>
@@ -465,9 +399,6 @@
     <t>Monarda punctata</t>
   </si>
   <si>
-    <t>Horse mint</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/bDD1pQ5z/Horse-mint.jpg</t>
   </si>
   <si>
@@ -480,9 +411,6 @@
     <t>Plectranthus amboinicus</t>
   </si>
   <si>
-    <t xml:space="preserve">Mexican Mint </t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/VS5CWqmj/Mexican-mint.jpg</t>
   </si>
   <si>
@@ -495,9 +423,6 @@
     <t>Salvia officinalis</t>
   </si>
   <si>
-    <t>Common Sage</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/gx7ywzZc/common-sage.jpg</t>
   </si>
   <si>
@@ -510,9 +435,6 @@
     <t xml:space="preserve">Thymus vulgaris </t>
   </si>
   <si>
-    <t xml:space="preserve">Thymus </t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/8FrRM2RR/Thymus.avif</t>
   </si>
   <si>
@@ -525,9 +447,6 @@
     <t xml:space="preserve">Mentha spicata </t>
   </si>
   <si>
-    <t>Spearmint</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/w357JfLC/spearmint.jpg</t>
   </si>
   <si>
@@ -540,9 +459,6 @@
     <t>Salvia rosmarinus</t>
   </si>
   <si>
-    <t>Rosemary</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/njBM3T5Q/Rose-mary.jpg</t>
   </si>
   <si>
@@ -558,9 +474,6 @@
     <t>Pelargonium graveolens</t>
   </si>
   <si>
-    <t>Scented geranium</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/Mf0Mptm8/pelargonium.jpg</t>
   </si>
   <si>
@@ -573,9 +486,6 @@
     <t>Ixora coccinea</t>
   </si>
   <si>
-    <t>Flame of The Woods</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/8FWvjhGw/Flame-of-the-woods.jpg</t>
   </si>
   <si>
@@ -586,9 +496,6 @@
   </si>
   <si>
     <t>Ficus benjamina</t>
-  </si>
-  <si>
-    <t>Weeping Fig</t>
   </si>
   <si>
     <t>https://i.postimg.cc/Z9yqqVJD/WEEPING-FIG.jpg</t>
@@ -615,9 +522,6 @@
     </r>
   </si>
   <si>
-    <t>Yellow Butterfly Palm</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/G8wmTG23/Yellow-butterfly-palm.jpg</t>
   </si>
   <si>
@@ -630,9 +534,6 @@
     <t>Spathiphyllum</t>
   </si>
   <si>
-    <t>Peace Lily</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/n9f9xN7k/Peace-lily.jpg</t>
   </si>
   <si>
@@ -645,9 +546,6 @@
     <t xml:space="preserve">Anthurium andraeanum </t>
   </si>
   <si>
-    <t>Flamingo Flower</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/1nQq6f5S/Flamingo-Flower.jpg</t>
   </si>
   <si>
@@ -660,9 +558,6 @@
     <t>Dracaena sanderiana</t>
   </si>
   <si>
-    <t>Lucky Bamboo</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/QV7czJ5m/Lucky-Bamboo.jpg</t>
   </si>
   <si>
@@ -678,9 +573,6 @@
     <t>Sansevieria trifasciata</t>
   </si>
   <si>
-    <t>Snake Plant</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/LgV5p5m9/Snake-plant.jpg</t>
   </si>
   <si>
@@ -696,9 +588,6 @@
     <t>Catharanthus roseus</t>
   </si>
   <si>
-    <t>Madagascar periwinkle</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/3dCm8rtD/Madagascar-periwinkle.jpg</t>
   </si>
   <si>
@@ -711,9 +600,6 @@
     <t>Ledebouria socialis</t>
   </si>
   <si>
-    <t>Silver squill</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/0KvjFDRX/Silver-squill.jpg</t>
   </si>
   <si>
@@ -729,9 +615,6 @@
     <t>Dieffenbachia seguine</t>
   </si>
   <si>
-    <t>Dieffenbachia</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/fJTYBt7T/Dieffenbachia.jpg</t>
   </si>
   <si>
@@ -744,9 +627,6 @@
     <t>Aglaonema commutatum</t>
   </si>
   <si>
-    <t>Chinees evergreen</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/mtbyJ644/Chinees-evergreen.jpg</t>
   </si>
   <si>
@@ -759,9 +639,6 @@
     <t>Philodendron xanadu</t>
   </si>
   <si>
-    <t>Xanadu</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/bd12gNcF/Philodendron-Xanadu.jpg</t>
   </si>
   <si>
@@ -774,9 +651,6 @@
     <t>Tradescantia spathacea</t>
   </si>
   <si>
-    <t>Oyster Plant</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/sMxXk3qz/Tradescantia-spathacea.jpg</t>
   </si>
   <si>
@@ -789,9 +663,6 @@
     <t>Sansevieria trifasciata var. laurentii</t>
   </si>
   <si>
-    <t>Variegated Snake Plant</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/5Xr01ZWC/Variegated-Snake-Plant.jpg</t>
   </si>
   <si>
@@ -804,9 +675,6 @@
     <t>Beaucarnea recurvata</t>
   </si>
   <si>
-    <t>Ponytail Palm</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/GHrT5wb3/Ponytail-Palm.jpg</t>
   </si>
   <si>
@@ -819,9 +687,6 @@
     <t>Chlorophytum comosum</t>
   </si>
   <si>
-    <t>Spider Plant</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/dL43NhWn/Spider-Plant.jpg</t>
   </si>
   <si>
@@ -834,9 +699,6 @@
     <t>Tradescantia pallida</t>
   </si>
   <si>
-    <t>Purple Heart</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/xX1J9vkW/Purple-Heart.jpg</t>
   </si>
   <si>
@@ -849,9 +711,6 @@
     <t>Dracaena cambodiana</t>
   </si>
   <si>
-    <t>Cambodian Dragon Tree</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/vD7vPwpX/Cambodian-Dragon-Tree.jpg</t>
   </si>
   <si>
@@ -864,9 +723,6 @@
     <t>Dracaena reflexa</t>
   </si>
   <si>
-    <t>Song of india</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/HjtQw4yh/Dracaena-reflexa-song-of-india.jpg</t>
   </si>
   <si>
@@ -879,9 +735,6 @@
     <t>Cycas revoluta</t>
   </si>
   <si>
-    <t>Sago Palm, King Sago, Japanese Sago</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/ZvJ6k01H/cycas-revoluta-sago-plam.jpg</t>
   </si>
   <si>
@@ -894,9 +747,6 @@
     <t>‏Portulaca umbraticola</t>
   </si>
   <si>
-    <t>Purslane</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/ry32bMjD/Portulaca-umbraticola.jpg</t>
   </si>
   <si>
@@ -909,9 +759,6 @@
     <t>Portulaca grandiflora</t>
   </si>
   <si>
-    <t>Moss rose</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/JzwNkSV2/Portulaca-grandiflora.jpg</t>
   </si>
   <si>
@@ -924,9 +771,6 @@
     <t xml:space="preserve">Rosa hybrida </t>
   </si>
   <si>
-    <t>Tea rose</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/svV1JYJv/Tea-rose.jpg</t>
   </si>
   <si>
@@ -939,9 +783,6 @@
     <t>Alternanthera brasiliana</t>
   </si>
   <si>
-    <t>Brazilian Joyweed</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/QVZbkdnH/Brazilian-Joyweed.jpg</t>
   </si>
   <si>
@@ -1084,6 +925,165 @@
   </si>
   <si>
     <t>Administration Building third floor</t>
+  </si>
+  <si>
+    <t>كركديه صيني</t>
+  </si>
+  <si>
+    <t>فيلوديندرون القلبي</t>
+  </si>
+  <si>
+    <t>إيوبيا</t>
+  </si>
+  <si>
+    <t>سينغونيوم</t>
+  </si>
+  <si>
+    <t>بوثوس ذهبي</t>
+  </si>
+  <si>
+    <t>سيندابسوس</t>
+  </si>
+  <si>
+    <t>أراوكاريا</t>
+  </si>
+  <si>
+    <t>رافينيا</t>
+  </si>
+  <si>
+    <t>شيفليرا</t>
+  </si>
+  <si>
+    <t>دراكينا</t>
+  </si>
+  <si>
+    <t>دراكينا ضيقة الأوراق</t>
+  </si>
+  <si>
+    <t>سانسيفيريا أسطوانية</t>
+  </si>
+  <si>
+    <t>باتشيرا</t>
+  </si>
+  <si>
+    <t>فيكس مطاطي</t>
+  </si>
+  <si>
+    <t>كروتون</t>
+  </si>
+  <si>
+    <t>فيكس ميكروكاربا</t>
+  </si>
+  <si>
+    <t>كلانشو</t>
+  </si>
+  <si>
+    <t>الجهنمية الجرداء</t>
+  </si>
+  <si>
+    <t>دراكينا عطرية</t>
+  </si>
+  <si>
+    <t>زاميا</t>
+  </si>
+  <si>
+    <t>خزامى</t>
+  </si>
+  <si>
+    <t>عشب الليمون</t>
+  </si>
+  <si>
+    <t>موناردا</t>
+  </si>
+  <si>
+    <t>بليكترا</t>
+  </si>
+  <si>
+    <t>مريمية</t>
+  </si>
+  <si>
+    <t>زعتر</t>
+  </si>
+  <si>
+    <t>نعناع أخضر</t>
+  </si>
+  <si>
+    <t>إكليل الجبل</t>
+  </si>
+  <si>
+    <t>جيرانيوم</t>
+  </si>
+  <si>
+    <t>إكسورا</t>
+  </si>
+  <si>
+    <t>فيكس بنجاميا</t>
+  </si>
+  <si>
+    <t>ديبسياس</t>
+  </si>
+  <si>
+    <t>زنبق السلام</t>
+  </si>
+  <si>
+    <t>أنثوريوم</t>
+  </si>
+  <si>
+    <t>دراكينا ساندر</t>
+  </si>
+  <si>
+    <t>نبات الثعبان</t>
+  </si>
+  <si>
+    <t>كاتارانثوس وردي</t>
+  </si>
+  <si>
+    <t>زنبق الفهد</t>
+  </si>
+  <si>
+    <t>ديفينباخيا</t>
+  </si>
+  <si>
+    <t>أجلونيما</t>
+  </si>
+  <si>
+    <t>فيلوديندرون زانادو</t>
+  </si>
+  <si>
+    <t>تريدسكينتيا</t>
+  </si>
+  <si>
+    <t>سانسيفيريا مخططة</t>
+  </si>
+  <si>
+    <t>بوكارنيا</t>
+  </si>
+  <si>
+    <t>نبات العنكبوت</t>
+  </si>
+  <si>
+    <t>تريدسكينتيا بنفسجية</t>
+  </si>
+  <si>
+    <t>دراكينا كمبودية</t>
+  </si>
+  <si>
+    <t>دراكينا منعكسة</t>
+  </si>
+  <si>
+    <t>سيكاس</t>
+  </si>
+  <si>
+    <t>بورتيولا</t>
+  </si>
+  <si>
+    <t>بورتيولا كبيرة الأزهار</t>
+  </si>
+  <si>
+    <t>ورد هجين</t>
+  </si>
+  <si>
+    <t>ألتيرنانثيرا برازيلية</t>
   </si>
 </sst>
 </file>
@@ -2495,1586 +2495,1586 @@
         <v>10</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>11</v>
+        <v>287</v>
       </c>
       <c r="D2" s="10" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Chinese%20Hibiscus.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="I2" s="28" t="s">
         <v>15</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>18</v>
-      </c>
       <c r="C3" s="9" t="s">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="D3" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/heartleaf.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="28" t="s">
         <v>20</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>25</v>
+        <v>289</v>
       </c>
       <c r="D4" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/crown%20of%20thorns.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>31</v>
+        <v>290</v>
       </c>
       <c r="D5" s="17" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Arrowhead.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H5" s="16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>36</v>
+        <v>291</v>
       </c>
       <c r="D6" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/golden%20phothos.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H6" s="9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>42</v>
+        <v>292</v>
       </c>
       <c r="D7" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Satin%20pothos.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H7" s="16" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>48</v>
+        <v>293</v>
       </c>
       <c r="D8" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Araucaria%20heterophylla-Norfolk%20Island%20pine.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H8" s="9" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>54</v>
+        <v>294</v>
       </c>
       <c r="D9" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Majestic%20Palm.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F9" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H9" s="16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I9" s="28" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>59</v>
+        <v>295</v>
       </c>
       <c r="D10" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Chinees%20evergreen.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I10" s="28" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>64</v>
+        <v>296</v>
       </c>
       <c r="D11" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Madagascar%20dragon%20tree.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F11" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H11" s="16" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>70</v>
+        <v>297</v>
       </c>
       <c r="D12" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/rainbow%20tree.jpg","Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>76</v>
+        <v>298</v>
       </c>
       <c r="D13" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/cylindrical%20snake%20plant.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="D14" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Money%20tree.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F14" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H14" s="9" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>87</v>
+        <v>300</v>
       </c>
       <c r="D15" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Rubber%20tree-Ficus%20elastica.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F15" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H15" s="9" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>93</v>
+        <v>301</v>
       </c>
       <c r="D16" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Codiaeum%20variegatum-Garden%20croton.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I16" s="28" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>98</v>
+        <v>302</v>
       </c>
       <c r="D17" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Ficus%20microcarpa.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I17" s="28" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>103</v>
+        <v>303</v>
       </c>
       <c r="D18" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Kalanchoe%20blossfeldiana.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>109</v>
+        <v>304</v>
       </c>
       <c r="D19" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Paper%20flower.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="I19" s="28" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>115</v>
+        <v>305</v>
       </c>
       <c r="D20" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Corn%20Plant.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="F20" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H20" s="16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I20" s="28" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>120</v>
+        <v>306</v>
       </c>
       <c r="D21" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Zanzibar%20Gem%20(2).jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="I21" s="28" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>127</v>
+        <v>307</v>
       </c>
       <c r="D22" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/English%20lavender.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="I22" s="28" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>132</v>
+        <v>308</v>
       </c>
       <c r="D23" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/LEMON%20GRASS.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="I23" s="28" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>137</v>
+        <v>309</v>
       </c>
       <c r="D24" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Horse%20mint.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="I24" s="28" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>142</v>
+        <v>310</v>
       </c>
       <c r="D25" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Mexican%20mint.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I25" s="28" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>147</v>
+        <v>311</v>
       </c>
       <c r="D26" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/common%20sage.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="I26" s="28" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>152</v>
+        <v>312</v>
       </c>
       <c r="D27" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/thymus.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>157</v>
+        <v>313</v>
       </c>
       <c r="D28" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/spearmint.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>162</v>
+        <v>314</v>
       </c>
       <c r="D29" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Rose%20mary.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="I29" s="28" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>168</v>
+        <v>315</v>
       </c>
       <c r="D30" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/pelargonium.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I30" s="28" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>173</v>
+        <v>316</v>
       </c>
       <c r="D31" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Flame%20of%20the%20woods.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="I31" s="28" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>178</v>
+        <v>317</v>
       </c>
       <c r="D32" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/WEEPING%20FIG.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="I32" s="28" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>183</v>
+        <v>318</v>
       </c>
       <c r="D33" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Yellow%20butterfly%20palm.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="I33" s="28" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>188</v>
+        <v>319</v>
       </c>
       <c r="D34" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Peace%20lily.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I34" s="28" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>193</v>
+        <v>320</v>
       </c>
       <c r="D35" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Flamingo%20Flower.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="I35" s="28" t="s">
-        <v>195</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>198</v>
+        <v>321</v>
       </c>
       <c r="D36" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Lucky%20Bamboo.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="I36" s="28" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>204</v>
+        <v>322</v>
       </c>
       <c r="D37" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Snake%20plant.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="I37" s="28" t="s">
-        <v>207</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>210</v>
+        <v>323</v>
       </c>
       <c r="D38" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Madagascar%20dragon%20tree.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="I38" s="28" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>215</v>
+        <v>324</v>
       </c>
       <c r="D39" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Silver%20squill.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="F39" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H39" s="16" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="I39" s="28" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>221</v>
+        <v>325</v>
       </c>
       <c r="D40" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Dieffenbachia.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="F40" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G40" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H40" s="16" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I40" s="28" t="s">
-        <v>223</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>226</v>
+        <v>326</v>
       </c>
       <c r="D41" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Chinees%20evergreen.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="F41" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H41" s="16" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I41" s="28" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>231</v>
+        <v>327</v>
       </c>
       <c r="D42" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Philodendron%20Xanadu.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>232</v>
+        <v>191</v>
       </c>
       <c r="F42" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H42" s="9" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="I42" s="28" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>236</v>
+        <v>328</v>
       </c>
       <c r="D43" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Tradescantia%20spathacea.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="F43" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G43" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H43" s="20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I43" s="28" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="D44" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Variegated%20Snake%20Plant.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="F44" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="H44" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H44" s="9" t="s">
-        <v>15</v>
-      </c>
       <c r="I44" s="28" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>246</v>
+        <v>330</v>
       </c>
       <c r="D45" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Ponytail%20Palm.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>247</v>
+        <v>203</v>
       </c>
       <c r="F45" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H45" s="9" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="I45" s="28" t="s">
-        <v>248</v>
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>251</v>
+        <v>331</v>
       </c>
       <c r="D46" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Spider%20Plant.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>252</v>
+        <v>207</v>
       </c>
       <c r="F46" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G46" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H46" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I46" s="28" t="s">
-        <v>253</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>256</v>
+        <v>332</v>
       </c>
       <c r="D47" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Purple%20Heart.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
       <c r="F47" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H47" s="9" t="s">
-        <v>15</v>
-      </c>
       <c r="I47" s="28" t="s">
-        <v>258</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>261</v>
+        <v>333</v>
       </c>
       <c r="D48" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Cambodian%20Dragon%20Tree.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>262</v>
+        <v>215</v>
       </c>
       <c r="F48" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G48" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H48" s="9" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="I48" s="28" t="s">
-        <v>263</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
-        <v>264</v>
+        <v>217</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>266</v>
+        <v>334</v>
       </c>
       <c r="D49" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Dracaena%20reflexa%20(%20song%20of%20india).jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
       <c r="F49" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G49" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H49" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I49" s="28" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="D50" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/cycas%20revoluta%20(sago%20plam).jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c r="F50" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G50" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H50" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I50" s="28" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
-        <v>274</v>
+        <v>225</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>276</v>
+        <v>336</v>
       </c>
       <c r="D51" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/%E2%80%8FPortulaca%20umbraticola.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>277</v>
+        <v>227</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H51" s="21" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="I51" s="28" t="s">
-        <v>278</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>279</v>
+        <v>229</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>281</v>
+        <v>337</v>
       </c>
       <c r="D52" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Portulaca%20grandiflora.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="I52" s="28" t="s">
-        <v>283</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>285</v>
+        <v>234</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="D53" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Tea%20rose.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="I53" s="28" t="s">
-        <v>288</v>
+        <v>236</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
-        <v>289</v>
+        <v>237</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>290</v>
+        <v>238</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
       <c r="D54" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Brazilian%20Joyweed.jpeg","Open Image ")</f>
         <v xml:space="preserve">Open Image </v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="F54" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G54" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="H54" s="22" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="I54" s="28" t="s">
-        <v>293</v>
+        <v>240</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
@@ -4374,16 +4374,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>294</v>
+        <v>241</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>296</v>
+        <v>243</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>297</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -4395,13 +4395,13 @@
         <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -4414,16 +4414,16 @@
         <v>IP-002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F3" s="2">
         <v>4</v>
@@ -4435,16 +4435,16 @@
         <v>IP-003</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F4" s="2">
         <v>10</v>
@@ -4456,16 +4456,16 @@
         <v>IP-005</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>303</v>
+        <v>250</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F5" s="2">
         <v>24</v>
@@ -4477,16 +4477,16 @@
         <v>IP-008</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>303</v>
+        <v>250</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -4498,16 +4498,16 @@
         <v>IP-009</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>303</v>
+        <v>250</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F7" s="2">
         <v>7</v>
@@ -4519,16 +4519,16 @@
         <v>IP-010</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F8" s="2">
         <v>3</v>
@@ -4540,16 +4540,16 @@
         <v>IP-011</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -4561,16 +4561,16 @@
         <v>IP-013</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F10" s="2">
         <v>8</v>
@@ -4582,16 +4582,16 @@
         <v>IP-014</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F11" s="2">
         <v>2</v>
@@ -4603,16 +4603,16 @@
         <v>IP-015</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
@@ -4624,16 +4624,16 @@
         <v>IP-016</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F13" s="2">
         <v>16</v>
@@ -4645,16 +4645,16 @@
         <v>IP-019</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F14" s="2">
         <v>10</v>
@@ -4666,16 +4666,16 @@
         <v>IP-021</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>304</v>
+        <v>251</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -4687,16 +4687,16 @@
         <v>IP-022</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -4708,16 +4708,16 @@
         <v>IP-023</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
@@ -4729,16 +4729,16 @@
         <v>IP-024</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
@@ -4750,16 +4750,16 @@
         <v>IP-025</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -4771,16 +4771,16 @@
         <v>IP-030</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F20" s="2">
         <v>5</v>
@@ -4792,16 +4792,16 @@
         <v>IP-031</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F21" s="2">
         <v>8</v>
@@ -4813,16 +4813,16 @@
         <v>IP-032</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>306</v>
+        <v>253</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F22" s="2">
         <v>12</v>
@@ -4834,16 +4834,16 @@
         <v>IP-033</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F23" s="2">
         <v>1</v>
@@ -4855,16 +4855,16 @@
         <v>IP-034</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F24" s="2">
         <v>1</v>
@@ -4876,16 +4876,16 @@
         <v>IP-035</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F25" s="2">
         <v>2</v>
@@ -4897,16 +4897,16 @@
         <v>IP-047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F26" s="2">
         <v>9</v>
@@ -4918,16 +4918,16 @@
         <v>IP-031</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F27" s="2">
         <v>26</v>
@@ -4939,16 +4939,16 @@
         <v>IP-005</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="F28" s="2">
         <v>15</v>
@@ -4960,16 +4960,16 @@
         <v>IP-005</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>307</v>
+        <v>254</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c r="F29" s="2">
         <v>14</v>
@@ -4981,16 +4981,16 @@
         <v>IP-009</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>309</v>
+        <v>256</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="F30" s="2">
         <v>2</v>
@@ -5002,16 +5002,16 @@
         <v>IP-016</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>309</v>
+        <v>256</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="F31" s="2">
         <v>4</v>
@@ -5023,16 +5023,16 @@
         <v>IP-047</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>309</v>
+        <v>256</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -5044,16 +5044,16 @@
         <v>IP-010</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>309</v>
+        <v>256</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="F33" s="2">
         <v>2</v>
@@ -5065,16 +5065,16 @@
         <v>IP-005</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>311</v>
+        <v>258</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>312</v>
+        <v>259</v>
       </c>
       <c r="F34" s="2">
         <v>2</v>
@@ -5086,16 +5086,16 @@
         <v>IP-020</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>311</v>
+        <v>258</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>312</v>
+        <v>259</v>
       </c>
       <c r="F35" s="2">
         <v>4</v>
@@ -5107,16 +5107,16 @@
         <v>IP-010</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>311</v>
+        <v>258</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>312</v>
+        <v>259</v>
       </c>
       <c r="F36" s="2">
         <v>2</v>
@@ -5128,16 +5128,16 @@
         <v>IP-016</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>307</v>
+        <v>254</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c r="F37" s="2">
         <v>4</v>
@@ -5149,16 +5149,16 @@
         <v>IP-031</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>307</v>
+        <v>254</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c r="F38" s="2">
         <v>4</v>
@@ -5170,16 +5170,16 @@
         <v>IP-036</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>307</v>
+        <v>254</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c r="F39" s="2">
         <v>1</v>
@@ -5191,16 +5191,16 @@
         <v>IP-004</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>307</v>
+        <v>254</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
@@ -5212,16 +5212,16 @@
         <v>IP-005</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>313</v>
+        <v>260</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>314</v>
+        <v>261</v>
       </c>
       <c r="F41" s="2">
         <v>2</v>
@@ -5233,16 +5233,16 @@
         <v>IP-005</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>315</v>
+        <v>262</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>316</v>
+        <v>263</v>
       </c>
       <c r="F42" s="2">
         <v>6</v>
@@ -5254,16 +5254,16 @@
         <v>IP-014</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="F43" s="2">
         <v>1</v>
@@ -5275,16 +5275,16 @@
         <v>IP-020</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="F44" s="2">
         <v>3</v>
@@ -5296,16 +5296,16 @@
         <v>IP-009</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="F45" s="2">
         <v>2</v>
@@ -5317,16 +5317,16 @@
         <v>IP-031</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="F46" s="2">
         <v>4</v>
@@ -5338,16 +5338,16 @@
         <v>IP-005</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -5359,16 +5359,16 @@
         <v>IP-019</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="F48" s="2">
         <v>1</v>
@@ -5380,16 +5380,16 @@
         <v>IP-003</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="F49" s="2">
         <v>2</v>
@@ -5401,16 +5401,16 @@
         <v>IP-005</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>320</v>
+        <v>267</v>
       </c>
       <c r="F50" s="2">
         <v>6</v>
@@ -5422,16 +5422,16 @@
         <v>IP-031</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="F51" s="2">
         <v>20</v>
@@ -5443,16 +5443,16 @@
         <v>IP-016</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="F52" s="2">
         <v>10</v>
@@ -5464,16 +5464,16 @@
         <v>IP-013</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="F53" s="2">
         <v>1</v>
@@ -5485,16 +5485,16 @@
         <v>IP-047</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="F54" s="2">
         <v>1</v>
@@ -5506,16 +5506,16 @@
         <v>IP-005</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="F55" s="2">
         <v>10</v>
@@ -5527,16 +5527,16 @@
         <v>IP-020</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="F56" s="2">
         <v>5</v>
@@ -5548,16 +5548,16 @@
         <v>IP-019</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="F57" s="2">
         <v>3</v>
@@ -5569,16 +5569,16 @@
         <v>IP-005</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>323</v>
+        <v>270</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="F58" s="2">
         <v>8</v>
@@ -5590,16 +5590,16 @@
         <v>IP-020</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>323</v>
+        <v>270</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="F59" s="2">
         <v>4</v>
@@ -5611,16 +5611,16 @@
         <v>IP-019</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>323</v>
+        <v>270</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="F60" s="2">
         <v>6</v>
@@ -5632,16 +5632,16 @@
         <v>IP-014</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>323</v>
+        <v>270</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="F61" s="2">
         <v>1</v>
@@ -5653,16 +5653,16 @@
         <v>IP-040</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>323</v>
+        <v>270</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="F62" s="2">
         <v>1</v>
@@ -5674,16 +5674,16 @@
         <v>IP-010</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>313</v>
+        <v>260</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>314</v>
+        <v>261</v>
       </c>
       <c r="F63" s="2">
         <v>2</v>
@@ -5695,16 +5695,16 @@
         <v>IP-019</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>313</v>
+        <v>260</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>314</v>
+        <v>261</v>
       </c>
       <c r="F64" s="2">
         <v>2</v>
@@ -5716,16 +5716,16 @@
         <v>IP-031</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>313</v>
+        <v>260</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>314</v>
+        <v>261</v>
       </c>
       <c r="F65" s="2">
         <v>6</v>
@@ -5737,16 +5737,16 @@
         <v>IP-014</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>313</v>
+        <v>260</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>314</v>
+        <v>261</v>
       </c>
       <c r="F66" s="2">
         <v>1</v>
@@ -5758,16 +5758,16 @@
         <v>IP-005</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="F67" s="2">
         <v>4</v>
@@ -5779,16 +5779,16 @@
         <v>IP-014</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="F68" s="2">
         <v>1</v>
@@ -5800,16 +5800,16 @@
         <v>IP-019</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="F69" s="2">
         <v>2</v>
@@ -5821,16 +5821,16 @@
         <v>IP-031</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="F70" s="2">
         <v>20</v>
@@ -5842,16 +5842,16 @@
         <v>IP-016</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="F71" s="2">
         <v>10</v>
@@ -5863,16 +5863,16 @@
         <v>IP-036</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>320</v>
+        <v>267</v>
       </c>
       <c r="F72" s="2">
         <v>1</v>
@@ -5884,16 +5884,16 @@
         <v>IP-019</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>320</v>
+        <v>267</v>
       </c>
       <c r="F73" s="2">
         <v>10</v>
@@ -5905,16 +5905,16 @@
         <v>IP-031</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>320</v>
+        <v>267</v>
       </c>
       <c r="F74" s="2">
         <v>2</v>
@@ -5926,16 +5926,16 @@
         <v>IP-020</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>320</v>
+        <v>267</v>
       </c>
       <c r="F75" s="2">
         <v>2</v>
@@ -5947,16 +5947,16 @@
         <v>IP-014</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>320</v>
+        <v>267</v>
       </c>
       <c r="F76" s="2">
         <v>1</v>
@@ -5968,16 +5968,16 @@
         <v>IP-020</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F77" s="2">
         <v>7</v>
@@ -5989,16 +5989,16 @@
         <v>IP-014</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F78" s="2">
         <v>2</v>
@@ -6010,16 +6010,16 @@
         <v>IP-016</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F79" s="2">
         <v>1</v>
@@ -6031,16 +6031,16 @@
         <v>IP-045</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F80" s="2">
         <v>1</v>
@@ -6052,16 +6052,16 @@
         <v>IP-007</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F81" s="2">
         <v>1</v>
@@ -6073,16 +6073,16 @@
         <v>IP-019</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F82" s="2">
         <v>3</v>
@@ -6094,16 +6094,16 @@
         <v>IP-010</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F83" s="2">
         <v>1</v>
@@ -6115,16 +6115,16 @@
         <v>IP-009</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F84" s="2">
         <v>2</v>
@@ -6136,16 +6136,16 @@
         <v>IP-007</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F85" s="2">
         <v>1</v>
@@ -6157,16 +6157,16 @@
         <v>IP-036</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F86" s="2">
         <v>1</v>
@@ -6178,16 +6178,16 @@
         <v>IP-035</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F87" s="2">
         <v>2</v>
@@ -6199,16 +6199,16 @@
         <v>IP-036</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F88" s="2">
         <v>1</v>
@@ -6220,16 +6220,16 @@
         <v>IP-005</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F89" s="2">
         <v>4</v>
@@ -6241,16 +6241,16 @@
         <v>IP-002</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="F90" s="2">
         <v>1</v>
@@ -6262,16 +6262,16 @@
         <v>IP-019</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="F91" s="2">
         <v>2</v>
@@ -6283,16 +6283,16 @@
         <v>IP-039</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="F92" s="2">
         <v>2</v>
@@ -6304,16 +6304,16 @@
         <v>IP-005</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="F93" s="2">
         <v>2</v>
@@ -6325,16 +6325,16 @@
         <v>IP-046</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="F94" s="2">
         <v>1</v>
@@ -6346,16 +6346,16 @@
         <v>IP-040</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="F95" s="2">
         <v>1</v>
@@ -6367,16 +6367,16 @@
         <v>IP-036</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="F96" s="2">
         <v>1</v>
@@ -6388,16 +6388,16 @@
         <v>IP-019</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>331</v>
+        <v>278</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>332</v>
+        <v>279</v>
       </c>
       <c r="F97" s="2">
         <v>5</v>
@@ -6409,16 +6409,16 @@
         <v>IP-039</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F98" s="2">
         <v>1</v>
@@ -6430,16 +6430,16 @@
         <v>IP-041</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F99" s="2">
         <v>1</v>
@@ -6451,16 +6451,16 @@
         <v>IP-040</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F100" s="2">
         <v>2</v>
@@ -6472,16 +6472,16 @@
         <v>IP-037</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F101" s="2">
         <v>1</v>
@@ -6493,16 +6493,16 @@
         <v>IP-020</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F102" s="2">
         <v>1</v>
@@ -6514,16 +6514,16 @@
         <v>IP-018</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F103" s="2">
         <v>1</v>
@@ -6535,16 +6535,16 @@
         <v>IP-019</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F104" s="2">
         <v>1</v>
@@ -6556,16 +6556,16 @@
         <v>IP-052</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>285</v>
+        <v>234</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F105" s="2">
         <v>1</v>
@@ -6577,16 +6577,16 @@
         <v>IP-043</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F106" s="2">
         <v>1</v>
@@ -6598,16 +6598,16 @@
         <v>IP-036</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F107" s="2">
         <v>3</v>
@@ -6619,16 +6619,16 @@
         <v>IP-002</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F108" s="2">
         <v>1</v>
@@ -6640,16 +6640,16 @@
         <v>IP-039</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="F109" s="2">
         <v>1</v>
@@ -6661,16 +6661,16 @@
         <v>IP-045</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>334</v>
+        <v>281</v>
       </c>
       <c r="F110" s="2">
         <v>9</v>
@@ -6682,16 +6682,16 @@
         <v>IP-014</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F111" s="2">
         <v>6</v>
@@ -6703,16 +6703,16 @@
         <v>IP-043</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F112" s="2">
         <v>10</v>
@@ -6724,16 +6724,16 @@
         <v>IP-020</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F113" s="2">
         <v>6</v>
@@ -6745,16 +6745,16 @@
         <v>IP-041</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F114" s="2">
         <v>2</v>
@@ -6766,16 +6766,16 @@
         <v>IP-031</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F115" s="2">
         <v>5</v>
@@ -6787,16 +6787,16 @@
         <v>IP-005</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F116" s="2">
         <v>3</v>
@@ -6808,16 +6808,16 @@
         <v>IP-042</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F117" s="2">
         <v>1</v>
@@ -6829,16 +6829,16 @@
         <v>IP-037</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F118" s="2">
         <v>1</v>
@@ -6850,16 +6850,16 @@
         <v>IP-038</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F119" s="2">
         <v>8</v>
@@ -6871,16 +6871,16 @@
         <v>IP-019</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F120" s="2">
         <v>1</v>
@@ -6892,16 +6892,16 @@
         <v>IP-017</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F121" s="2">
         <v>2</v>
@@ -6913,16 +6913,16 @@
         <v>IP-035</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F122" s="2">
         <v>1</v>
@@ -6934,16 +6934,16 @@
         <v>IP-032</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>306</v>
+        <v>253</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F123" s="2">
         <v>1</v>
@@ -6955,16 +6955,16 @@
         <v>IP-036</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F124" s="2">
         <v>6</v>
@@ -6976,16 +6976,16 @@
         <v>IP-033</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F125" s="2">
         <v>1</v>
@@ -6997,16 +6997,16 @@
         <v>IP-039</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F126" s="2">
         <v>1</v>
@@ -7018,16 +7018,16 @@
         <v>IP-012</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F127" s="2">
         <v>1</v>
@@ -7039,16 +7039,16 @@
         <v>IP-009</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F128" s="2">
         <v>5</v>
@@ -7060,16 +7060,16 @@
         <v>IP-006</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F129" s="2">
         <v>2</v>
@@ -7081,16 +7081,16 @@
         <v>IP-003</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="F130" s="2">
         <v>2</v>
@@ -7102,16 +7102,16 @@
         <v>IP-015</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="F131" s="2">
         <v>4</v>
@@ -7123,16 +7123,16 @@
         <v>IP-014</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="F132" s="2">
         <v>19</v>
@@ -7144,16 +7144,16 @@
         <v>IP-039</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="F133" s="2">
         <v>1</v>
@@ -7165,16 +7165,16 @@
         <v>IP-044</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="F134" s="2">
         <v>10</v>
@@ -7186,16 +7186,16 @@
         <v>IP-036</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="F135" s="2">
         <v>3</v>
@@ -7207,16 +7207,16 @@
         <v>IP-048</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="F136" s="2">
         <v>1</v>
@@ -7228,16 +7228,16 @@
         <v>IP-009</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="F137" s="2">
         <v>2</v>
@@ -7249,16 +7249,16 @@
         <v>IP-012</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="F138" s="2">
         <v>1</v>
@@ -7270,16 +7270,16 @@
         <v>IP-049</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="F139" s="2">
         <v>1</v>
@@ -7291,16 +7291,16 @@
         <v>IP-050</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="F140" s="2">
         <v>2</v>
@@ -7312,16 +7312,16 @@
         <v>IP-051</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="F141" s="2">
         <v>2</v>
@@ -7333,16 +7333,16 @@
         <v>IP-026</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="F142" s="2">
         <v>1</v>
@@ -7354,16 +7354,16 @@
         <v>IP-029</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="F143" s="2">
         <v>1</v>
@@ -7375,16 +7375,16 @@
         <v>IP-027</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="F144" s="2">
         <v>1</v>
@@ -7396,16 +7396,16 @@
         <v>IP-028</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="F145" s="2">
         <v>1</v>
@@ -7417,16 +7417,16 @@
         <v>IP-052</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>285</v>
+        <v>234</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="F146" s="2">
         <v>1</v>
@@ -7438,16 +7438,16 @@
         <v>IP-005</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E147" s="25" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="F147" s="2">
         <v>7</v>
@@ -7459,16 +7459,16 @@
         <v>IP-020</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E148" s="25" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="F148" s="2">
         <v>6</v>
@@ -7480,16 +7480,16 @@
         <v>IP-048</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E149" s="25" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="F149" s="2">
         <v>8</v>
@@ -7501,16 +7501,16 @@
         <v>IP-013</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E150" s="25" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="F150" s="2">
         <v>2</v>
@@ -7522,16 +7522,16 @@
         <v>IP-032</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>306</v>
+        <v>253</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E151" s="25" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="F151" s="2">
         <v>2</v>
@@ -7543,16 +7543,16 @@
         <v>IP-014</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E152" s="25" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="F152" s="2">
         <v>1</v>
@@ -7564,16 +7564,16 @@
         <v>IP-015</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E153" s="25" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="F153" s="2">
         <v>3</v>
@@ -7585,16 +7585,16 @@
         <v>IP-044</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E154" s="25" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="F154" s="2">
         <v>1</v>
@@ -7606,16 +7606,16 @@
         <v>IP-053</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>290</v>
+        <v>238</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E155" s="26" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="F155" s="2">
         <v>1</v>
@@ -7627,16 +7627,16 @@
         <v>IP-043</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="F156" s="2">
         <v>1</v>
@@ -7648,16 +7648,16 @@
         <v>IP-013</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="F157" s="2">
         <v>1</v>
@@ -7669,16 +7669,16 @@
         <v>IP-019</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="F158" s="2">
         <v>2</v>
@@ -7690,16 +7690,16 @@
         <v>IP-019</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>320</v>
+        <v>267</v>
       </c>
       <c r="F159" s="2">
         <v>5</v>
@@ -7711,16 +7711,16 @@
         <v>IP-008</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="F160" s="2">
         <v>1</v>
@@ -7732,16 +7732,16 @@
         <v>IP-047</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="F161" s="2">
         <v>2</v>
@@ -7753,16 +7753,16 @@
         <v>IP-032</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>306</v>
+        <v>253</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="F162" s="2">
         <v>1</v>
@@ -7774,16 +7774,16 @@
         <v>IP-015</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="F163" s="2">
         <v>1</v>
@@ -7795,16 +7795,16 @@
         <v>IP-005</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>320</v>
+        <v>267</v>
       </c>
       <c r="F164" s="2">
         <v>1</v>

--- a/data/Indoor plants.xlsx
+++ b/data/Indoor plants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E83758E-A7B6-4B44-84EE-48B7F6BE4D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480F4E72-767D-4FC1-AF70-593AD41BF7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="345">
   <si>
     <t>Plant ID</t>
   </si>
@@ -372,21 +372,6 @@
     <t>IP-022</t>
   </si>
   <si>
-    <r>
-      <t>Cymbopogon citratus</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>https://i.postimg.cc/WhP0cqwv/LEMON-GRASS.jpg</t>
   </si>
   <si>
@@ -507,21 +492,6 @@
     <t>IP-032</t>
   </si>
   <si>
-    <r>
-      <t>Dypsis lutescens</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>https://i.postimg.cc/G8wmTG23/Yellow-butterfly-palm.jpg</t>
   </si>
   <si>
@@ -1084,13 +1054,34 @@
   </si>
   <si>
     <t>ألتيرنانثيرا برازيلية</t>
+  </si>
+  <si>
+    <t>Lavandula angustifolia</t>
+  </si>
+  <si>
+    <t>Cymbopogon citratus</t>
+  </si>
+  <si>
+    <t>Thymus vulgaris</t>
+  </si>
+  <si>
+    <t>Mentha spicata</t>
+  </si>
+  <si>
+    <t>Dypsis lutescens</t>
+  </si>
+  <si>
+    <t>Anthurium andraeanum</t>
+  </si>
+  <si>
+    <t>Rosa hybrida</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1156,20 +1147,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FF242424"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -2495,7 +2472,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D2" s="10" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Chinese%20Hibiscus.jpg", "Open Image")</f>
@@ -2525,7 +2502,7 @@
         <v>17</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D3" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/heartleaf.jpg", "Open Image")</f>
@@ -2555,7 +2532,7 @@
         <v>22</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D4" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/crown%20of%20thorns.jpg", "Open Image")</f>
@@ -2585,7 +2562,7 @@
         <v>27</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D5" s="17" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Arrowhead.jpg", "Open Image")</f>
@@ -2615,7 +2592,7 @@
         <v>31</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D6" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/golden%20phothos.jpg", "Open Image")</f>
@@ -2645,7 +2622,7 @@
         <v>36</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D7" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Satin%20pothos.jpg", "Open Image")</f>
@@ -2675,7 +2652,7 @@
         <v>41</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D8" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Araucaria%20heterophylla-Norfolk%20Island%20pine.jpg", "Open Image")</f>
@@ -2705,7 +2682,7 @@
         <v>46</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D9" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Majestic%20Palm.jpg", "Open Image")</f>
@@ -2735,7 +2712,7 @@
         <v>50</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D10" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Chinees%20evergreen.jpg", "Open Image")</f>
@@ -2765,7 +2742,7 @@
         <v>54</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D11" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Madagascar%20dragon%20tree.jpg", "Open Image")</f>
@@ -2795,7 +2772,7 @@
         <v>59</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D12" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/rainbow%20tree.jpg","Open Image")</f>
@@ -2825,7 +2802,7 @@
         <v>64</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D13" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/cylindrical%20snake%20plant.jpg", "Open Image")</f>
@@ -2855,7 +2832,7 @@
         <v>68</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D14" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Money%20tree.jpg", "Open Image")</f>
@@ -2885,7 +2862,7 @@
         <v>73</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D15" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Rubber%20tree-Ficus%20elastica.jpg", "Open Image")</f>
@@ -2915,7 +2892,7 @@
         <v>78</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D16" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Codiaeum%20variegatum-Garden%20croton.jpg", "Open Image")</f>
@@ -2945,7 +2922,7 @@
         <v>82</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D17" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Ficus%20microcarpa.jpg", "Open Image")</f>
@@ -2975,7 +2952,7 @@
         <v>86</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D18" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Kalanchoe%20blossfeldiana.jpg", "Open Image")</f>
@@ -3005,7 +2982,7 @@
         <v>91</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D19" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Paper%20flower.jpg", "Open Image")</f>
@@ -3035,7 +3012,7 @@
         <v>96</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D20" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Corn%20Plant.jpeg", "Open Image")</f>
@@ -3065,7 +3042,7 @@
         <v>100</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D21" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Zanzibar%20Gem%20(2).jpeg", "Open Image")</f>
@@ -3092,10 +3069,10 @@
         <v>105</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>106</v>
+        <v>338</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D22" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/English%20lavender.jpeg", "Open Image")</f>
@@ -3122,17 +3099,17 @@
         <v>109</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>110</v>
+        <v>339</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D23" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/LEMON%20GRASS.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>12</v>
@@ -3144,25 +3121,25 @@
         <v>93</v>
       </c>
       <c r="I23" s="28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>114</v>
-      </c>
       <c r="C24" s="9" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D24" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Horse%20mint.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>12</v>
@@ -3174,25 +3151,25 @@
         <v>103</v>
       </c>
       <c r="I24" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>118</v>
-      </c>
       <c r="C25" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D25" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Mexican%20mint.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>12</v>
@@ -3204,25 +3181,25 @@
         <v>14</v>
       </c>
       <c r="I25" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>122</v>
-      </c>
       <c r="C26" s="9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D26" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/common%20sage.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>12</v>
@@ -3234,25 +3211,25 @@
         <v>75</v>
       </c>
       <c r="I26" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>126</v>
+        <v>340</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D27" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/thymus.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>12</v>
@@ -3264,25 +3241,25 @@
         <v>75</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>130</v>
+        <v>341</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D28" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/spearmint.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>12</v>
@@ -3294,25 +3271,25 @@
         <v>38</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>134</v>
-      </c>
       <c r="C29" s="9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D29" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Rose%20mary.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>12</v>
@@ -3321,28 +3298,28 @@
         <v>24</v>
       </c>
       <c r="H29" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="I29" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I29" s="28" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>139</v>
-      </c>
       <c r="C30" s="9" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D30" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/pelargonium.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>12</v>
@@ -3354,25 +3331,25 @@
         <v>38</v>
       </c>
       <c r="I30" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>143</v>
-      </c>
       <c r="C31" s="9" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D31" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Flame%20of%20the%20woods.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>12</v>
@@ -3384,25 +3361,25 @@
         <v>93</v>
       </c>
       <c r="I31" s="28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>147</v>
-      </c>
       <c r="C32" s="9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D32" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/WEEPING%20FIG.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>12</v>
@@ -3414,25 +3391,25 @@
         <v>61</v>
       </c>
       <c r="I32" s="28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>151</v>
+        <v>342</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D33" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Yellow%20butterfly%20palm.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>12</v>
@@ -3444,25 +3421,25 @@
         <v>103</v>
       </c>
       <c r="I33" s="28" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D34" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Peace%20lily.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>12</v>
@@ -3474,25 +3451,25 @@
         <v>19</v>
       </c>
       <c r="I34" s="28" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D35" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Flamingo%20Flower.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>12</v>
@@ -3504,25 +3481,25 @@
         <v>61</v>
       </c>
       <c r="I35" s="28" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D36" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Lucky%20Bamboo.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>12</v>
@@ -3531,28 +3508,28 @@
         <v>24</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I36" s="28" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D37" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Snake%20plant.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>12</v>
@@ -3561,28 +3538,28 @@
         <v>102</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I37" s="28" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D38" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Madagascar%20dragon%20tree.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F38" s="12" t="s">
         <v>12</v>
@@ -3594,25 +3571,25 @@
         <v>93</v>
       </c>
       <c r="I38" s="28" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D39" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Silver%20squill.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>12</v>
@@ -3621,28 +3598,28 @@
         <v>13</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I39" s="28" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D40" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Dieffenbachia.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>12</v>
@@ -3654,25 +3631,25 @@
         <v>38</v>
       </c>
       <c r="I40" s="28" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D41" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Chinees%20evergreen.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>12</v>
@@ -3684,25 +3661,25 @@
         <v>38</v>
       </c>
       <c r="I41" s="28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D42" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Philodendron%20Xanadu.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>12</v>
@@ -3714,25 +3691,25 @@
         <v>103</v>
       </c>
       <c r="I42" s="28" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D43" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Tradescantia%20spathacea.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>12</v>
@@ -3744,25 +3721,25 @@
         <v>19</v>
       </c>
       <c r="I43" s="28" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D44" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Variegated%20Snake%20Plant.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F44" s="12" t="s">
         <v>12</v>
@@ -3774,25 +3751,25 @@
         <v>14</v>
       </c>
       <c r="I44" s="28" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D45" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Ponytail%20Palm.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>12</v>
@@ -3804,25 +3781,25 @@
         <v>103</v>
       </c>
       <c r="I45" s="28" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D46" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Spider%20Plant.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>12</v>
@@ -3834,25 +3811,25 @@
         <v>19</v>
       </c>
       <c r="I46" s="28" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D47" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Purple%20Heart.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>12</v>
@@ -3864,25 +3841,25 @@
         <v>14</v>
       </c>
       <c r="I47" s="28" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D48" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Cambodian%20Dragon%20Tree.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>12</v>
@@ -3894,25 +3871,25 @@
         <v>75</v>
       </c>
       <c r="I48" s="28" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D49" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Dracaena%20reflexa%20(%20song%20of%20india).jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>12</v>
@@ -3924,25 +3901,25 @@
         <v>19</v>
       </c>
       <c r="I49" s="28" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D50" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/cycas%20revoluta%20(sago%20plam).jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F50" s="12" t="s">
         <v>12</v>
@@ -3954,25 +3931,25 @@
         <v>19</v>
       </c>
       <c r="I50" s="28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D51" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/%E2%80%8FPortulaca%20umbraticola.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>12</v>
@@ -3981,28 +3958,28 @@
         <v>24</v>
       </c>
       <c r="H51" s="21" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I51" s="28" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D52" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Portulaca%20grandiflora.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>12</v>
@@ -4011,28 +3988,28 @@
         <v>24</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I52" s="28" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>234</v>
+        <v>344</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D53" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Tea%20rose.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>12</v>
@@ -4044,25 +4021,25 @@
         <v>75</v>
       </c>
       <c r="I53" s="28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D54" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Brazilian%20Joyweed.jpeg","Open Image ")</f>
         <v xml:space="preserve">Open Image </v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F54" s="12" t="s">
         <v>12</v>
@@ -4074,7 +4051,7 @@
         <v>93</v>
       </c>
       <c r="I54" s="28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
@@ -4225,7 +4202,7 @@
     <cfRule type="duplicateValues" dxfId="89" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54 B1:B26 B48:B50 B31:B46 B52 B56:B1048576">
-    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G35 G37:G1048576" xr:uid="{84F914E3-C5A8-4843-B3F4-1A37C7AF587E}">
@@ -4374,16 +4351,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -4395,13 +4372,13 @@
         <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -4417,13 +4394,13 @@
         <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F3" s="2">
         <v>4</v>
@@ -4438,13 +4415,13 @@
         <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F4" s="2">
         <v>10</v>
@@ -4459,13 +4436,13 @@
         <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F5" s="2">
         <v>24</v>
@@ -4480,13 +4457,13 @@
         <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -4501,13 +4478,13 @@
         <v>50</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F7" s="2">
         <v>7</v>
@@ -4522,13 +4499,13 @@
         <v>54</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F8" s="2">
         <v>3</v>
@@ -4543,13 +4520,13 @@
         <v>59</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -4564,13 +4541,13 @@
         <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F10" s="2">
         <v>8</v>
@@ -4585,13 +4562,13 @@
         <v>73</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F11" s="2">
         <v>2</v>
@@ -4606,13 +4583,13 @@
         <v>78</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
@@ -4627,13 +4604,13 @@
         <v>82</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F13" s="2">
         <v>16</v>
@@ -4648,13 +4625,13 @@
         <v>96</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F14" s="2">
         <v>10</v>
@@ -4663,19 +4640,19 @@
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="str">
         <f>_xlfn.XLOOKUP(B15, Sheet1!B:B, Sheet1!A:A, "Not Found")</f>
-        <v>IP-021</v>
+        <v>Not Found</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -4684,19 +4661,19 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="str">
         <f>_xlfn.XLOOKUP(B16, Sheet1!B:B, Sheet1!A:A, "Not Found")</f>
-        <v>IP-022</v>
+        <v>Not Found</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -4708,16 +4685,16 @@
         <v>IP-023</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
@@ -4729,16 +4706,16 @@
         <v>IP-024</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
@@ -4750,16 +4727,16 @@
         <v>IP-025</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -4771,16 +4748,16 @@
         <v>IP-030</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F20" s="2">
         <v>5</v>
@@ -4792,16 +4769,16 @@
         <v>IP-031</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F21" s="2">
         <v>8</v>
@@ -4810,19 +4787,19 @@
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="str">
         <f>_xlfn.XLOOKUP(B22, Sheet1!B:B, Sheet1!A:A, "Not Found")</f>
-        <v>IP-032</v>
+        <v>Not Found</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F22" s="2">
         <v>12</v>
@@ -4834,16 +4811,16 @@
         <v>IP-033</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F23" s="2">
         <v>1</v>
@@ -4852,19 +4829,19 @@
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="str">
         <f>_xlfn.XLOOKUP(B24, Sheet1!B:B, Sheet1!A:A, "Not Found")</f>
-        <v>IP-034</v>
+        <v>Not Found</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F24" s="2">
         <v>1</v>
@@ -4876,16 +4853,16 @@
         <v>IP-035</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F25" s="2">
         <v>2</v>
@@ -4897,16 +4874,16 @@
         <v>IP-047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F26" s="2">
         <v>9</v>
@@ -4918,16 +4895,16 @@
         <v>IP-031</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F27" s="2">
         <v>26</v>
@@ -4942,13 +4919,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F28" s="2">
         <v>15</v>
@@ -4963,13 +4940,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F29" s="2">
         <v>14</v>
@@ -4984,13 +4961,13 @@
         <v>50</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F30" s="2">
         <v>2</v>
@@ -5005,13 +4982,13 @@
         <v>82</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F31" s="2">
         <v>4</v>
@@ -5023,16 +5000,16 @@
         <v>IP-047</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -5047,13 +5024,13 @@
         <v>54</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F33" s="2">
         <v>2</v>
@@ -5068,13 +5045,13 @@
         <v>31</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F34" s="2">
         <v>2</v>
@@ -5089,13 +5066,13 @@
         <v>100</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F35" s="2">
         <v>4</v>
@@ -5110,13 +5087,13 @@
         <v>54</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F36" s="2">
         <v>2</v>
@@ -5131,13 +5108,13 @@
         <v>82</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F37" s="2">
         <v>4</v>
@@ -5149,16 +5126,16 @@
         <v>IP-031</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F38" s="2">
         <v>4</v>
@@ -5170,16 +5147,16 @@
         <v>IP-036</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F39" s="2">
         <v>1</v>
@@ -5194,13 +5171,13 @@
         <v>27</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
@@ -5215,13 +5192,13 @@
         <v>31</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F41" s="2">
         <v>2</v>
@@ -5236,13 +5213,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F42" s="2">
         <v>6</v>
@@ -5257,13 +5234,13 @@
         <v>73</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F43" s="2">
         <v>1</v>
@@ -5278,13 +5255,13 @@
         <v>100</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F44" s="2">
         <v>3</v>
@@ -5299,13 +5276,13 @@
         <v>50</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F45" s="2">
         <v>2</v>
@@ -5317,16 +5294,16 @@
         <v>IP-031</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F46" s="2">
         <v>4</v>
@@ -5341,13 +5318,13 @@
         <v>31</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -5362,13 +5339,13 @@
         <v>96</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F48" s="2">
         <v>1</v>
@@ -5383,13 +5360,13 @@
         <v>22</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F49" s="2">
         <v>2</v>
@@ -5404,13 +5381,13 @@
         <v>31</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F50" s="2">
         <v>6</v>
@@ -5422,16 +5399,16 @@
         <v>IP-031</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F51" s="2">
         <v>20</v>
@@ -5446,13 +5423,13 @@
         <v>82</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F52" s="2">
         <v>10</v>
@@ -5467,13 +5444,13 @@
         <v>68</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F53" s="2">
         <v>1</v>
@@ -5485,16 +5462,16 @@
         <v>IP-047</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F54" s="2">
         <v>1</v>
@@ -5509,13 +5486,13 @@
         <v>31</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F55" s="2">
         <v>10</v>
@@ -5530,13 +5507,13 @@
         <v>100</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F56" s="2">
         <v>5</v>
@@ -5551,13 +5528,13 @@
         <v>96</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F57" s="2">
         <v>3</v>
@@ -5572,13 +5549,13 @@
         <v>31</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F58" s="2">
         <v>8</v>
@@ -5593,13 +5570,13 @@
         <v>100</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F59" s="2">
         <v>4</v>
@@ -5614,13 +5591,13 @@
         <v>96</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F60" s="2">
         <v>6</v>
@@ -5635,13 +5612,13 @@
         <v>73</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F61" s="2">
         <v>1</v>
@@ -5653,16 +5630,16 @@
         <v>IP-040</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F62" s="2">
         <v>1</v>
@@ -5677,13 +5654,13 @@
         <v>54</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F63" s="2">
         <v>2</v>
@@ -5698,13 +5675,13 @@
         <v>96</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F64" s="2">
         <v>2</v>
@@ -5716,16 +5693,16 @@
         <v>IP-031</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F65" s="2">
         <v>6</v>
@@ -5740,13 +5717,13 @@
         <v>73</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F66" s="2">
         <v>1</v>
@@ -5761,13 +5738,13 @@
         <v>31</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F67" s="2">
         <v>4</v>
@@ -5782,13 +5759,13 @@
         <v>73</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F68" s="2">
         <v>1</v>
@@ -5803,13 +5780,13 @@
         <v>96</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F69" s="2">
         <v>2</v>
@@ -5821,16 +5798,16 @@
         <v>IP-031</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F70" s="2">
         <v>20</v>
@@ -5845,13 +5822,13 @@
         <v>82</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F71" s="2">
         <v>10</v>
@@ -5863,16 +5840,16 @@
         <v>IP-036</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F72" s="2">
         <v>1</v>
@@ -5887,13 +5864,13 @@
         <v>96</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F73" s="2">
         <v>10</v>
@@ -5905,16 +5882,16 @@
         <v>IP-031</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F74" s="2">
         <v>2</v>
@@ -5929,13 +5906,13 @@
         <v>100</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F75" s="2">
         <v>2</v>
@@ -5950,13 +5927,13 @@
         <v>73</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F76" s="2">
         <v>1</v>
@@ -5971,13 +5948,13 @@
         <v>100</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F77" s="2">
         <v>7</v>
@@ -5992,13 +5969,13 @@
         <v>73</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F78" s="2">
         <v>2</v>
@@ -6013,13 +5990,13 @@
         <v>82</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F79" s="2">
         <v>1</v>
@@ -6031,16 +6008,16 @@
         <v>IP-045</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F80" s="2">
         <v>1</v>
@@ -6055,13 +6032,13 @@
         <v>41</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F81" s="2">
         <v>1</v>
@@ -6076,13 +6053,13 @@
         <v>96</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F82" s="2">
         <v>3</v>
@@ -6097,13 +6074,13 @@
         <v>54</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F83" s="2">
         <v>1</v>
@@ -6118,13 +6095,13 @@
         <v>50</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F84" s="2">
         <v>2</v>
@@ -6139,13 +6116,13 @@
         <v>41</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F85" s="2">
         <v>1</v>
@@ -6157,16 +6134,16 @@
         <v>IP-036</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F86" s="2">
         <v>1</v>
@@ -6178,16 +6155,16 @@
         <v>IP-035</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F87" s="2">
         <v>2</v>
@@ -6199,16 +6176,16 @@
         <v>IP-036</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F88" s="2">
         <v>1</v>
@@ -6223,13 +6200,13 @@
         <v>31</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F89" s="2">
         <v>4</v>
@@ -6244,13 +6221,13 @@
         <v>17</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F90" s="2">
         <v>1</v>
@@ -6265,13 +6242,13 @@
         <v>96</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F91" s="2">
         <v>2</v>
@@ -6283,16 +6260,16 @@
         <v>IP-039</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F92" s="2">
         <v>2</v>
@@ -6307,13 +6284,13 @@
         <v>31</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F93" s="2">
         <v>2</v>
@@ -6325,16 +6302,16 @@
         <v>IP-046</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F94" s="2">
         <v>1</v>
@@ -6346,16 +6323,16 @@
         <v>IP-040</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F95" s="2">
         <v>1</v>
@@ -6367,16 +6344,16 @@
         <v>IP-036</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F96" s="2">
         <v>1</v>
@@ -6391,13 +6368,13 @@
         <v>96</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F97" s="2">
         <v>5</v>
@@ -6409,16 +6386,16 @@
         <v>IP-039</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C98" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F98" s="2">
         <v>1</v>
@@ -6430,16 +6407,16 @@
         <v>IP-041</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C99" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F99" s="2">
         <v>1</v>
@@ -6451,16 +6428,16 @@
         <v>IP-040</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C100" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F100" s="2">
         <v>2</v>
@@ -6472,16 +6449,16 @@
         <v>IP-037</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C101" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F101" s="2">
         <v>1</v>
@@ -6496,13 +6473,13 @@
         <v>100</v>
       </c>
       <c r="C102" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F102" s="2">
         <v>1</v>
@@ -6517,13 +6494,13 @@
         <v>91</v>
       </c>
       <c r="C103" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F103" s="2">
         <v>1</v>
@@ -6538,13 +6515,13 @@
         <v>96</v>
       </c>
       <c r="C104" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F104" s="2">
         <v>1</v>
@@ -6553,19 +6530,19 @@
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="str">
         <f>_xlfn.XLOOKUP(B105, Sheet1!B:B, Sheet1!A:A, "Not Found")</f>
-        <v>IP-052</v>
+        <v>Not Found</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C105" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F105" s="2">
         <v>1</v>
@@ -6577,16 +6554,16 @@
         <v>IP-043</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C106" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F106" s="2">
         <v>1</v>
@@ -6598,16 +6575,16 @@
         <v>IP-036</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C107" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F107" s="2">
         <v>3</v>
@@ -6622,13 +6599,13 @@
         <v>17</v>
       </c>
       <c r="C108" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F108" s="2">
         <v>1</v>
@@ -6640,16 +6617,16 @@
         <v>IP-039</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C109" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F109" s="2">
         <v>1</v>
@@ -6661,16 +6638,16 @@
         <v>IP-045</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F110" s="2">
         <v>9</v>
@@ -6685,13 +6662,13 @@
         <v>73</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D111" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F111" s="2">
         <v>6</v>
@@ -6703,16 +6680,16 @@
         <v>IP-043</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D112" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F112" s="2">
         <v>10</v>
@@ -6727,13 +6704,13 @@
         <v>100</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D113" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F113" s="2">
         <v>6</v>
@@ -6745,16 +6722,16 @@
         <v>IP-041</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D114" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F114" s="2">
         <v>2</v>
@@ -6766,16 +6743,16 @@
         <v>IP-031</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D115" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F115" s="2">
         <v>5</v>
@@ -6790,13 +6767,13 @@
         <v>31</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D116" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F116" s="2">
         <v>3</v>
@@ -6808,16 +6785,16 @@
         <v>IP-042</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D117" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F117" s="2">
         <v>1</v>
@@ -6829,16 +6806,16 @@
         <v>IP-037</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D118" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F118" s="2">
         <v>1</v>
@@ -6850,16 +6827,16 @@
         <v>IP-038</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D119" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F119" s="2">
         <v>8</v>
@@ -6874,13 +6851,13 @@
         <v>96</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D120" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F120" s="2">
         <v>1</v>
@@ -6895,13 +6872,13 @@
         <v>86</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D121" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E121" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F121" s="2">
         <v>2</v>
@@ -6913,16 +6890,16 @@
         <v>IP-035</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D122" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F122" s="2">
         <v>1</v>
@@ -6931,19 +6908,19 @@
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="str">
         <f>_xlfn.XLOOKUP(B123, Sheet1!B:B, Sheet1!A:A, "Not Found")</f>
-        <v>IP-032</v>
+        <v>Not Found</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D123" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F123" s="2">
         <v>1</v>
@@ -6955,16 +6932,16 @@
         <v>IP-036</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D124" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F124" s="2">
         <v>6</v>
@@ -6976,16 +6953,16 @@
         <v>IP-033</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D125" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F125" s="2">
         <v>1</v>
@@ -6997,16 +6974,16 @@
         <v>IP-039</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D126" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F126" s="2">
         <v>1</v>
@@ -7021,13 +6998,13 @@
         <v>64</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D127" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F127" s="2">
         <v>1</v>
@@ -7042,13 +7019,13 @@
         <v>50</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D128" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F128" s="2">
         <v>5</v>
@@ -7063,13 +7040,13 @@
         <v>36</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D129" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F129" s="2">
         <v>2</v>
@@ -7084,13 +7061,13 @@
         <v>22</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D130" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E130" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F130" s="2">
         <v>2</v>
@@ -7105,13 +7082,13 @@
         <v>78</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F131" s="2">
         <v>4</v>
@@ -7126,13 +7103,13 @@
         <v>73</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F132" s="2">
         <v>19</v>
@@ -7144,16 +7121,16 @@
         <v>IP-039</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F133" s="2">
         <v>1</v>
@@ -7165,16 +7142,16 @@
         <v>IP-044</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F134" s="2">
         <v>10</v>
@@ -7186,16 +7163,16 @@
         <v>IP-036</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F135" s="2">
         <v>3</v>
@@ -7207,16 +7184,16 @@
         <v>IP-048</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F136" s="2">
         <v>1</v>
@@ -7231,13 +7208,13 @@
         <v>50</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F137" s="2">
         <v>2</v>
@@ -7252,13 +7229,13 @@
         <v>64</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F138" s="2">
         <v>1</v>
@@ -7270,16 +7247,16 @@
         <v>IP-049</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F139" s="2">
         <v>1</v>
@@ -7291,16 +7268,16 @@
         <v>IP-050</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F140" s="2">
         <v>2</v>
@@ -7312,16 +7289,16 @@
         <v>IP-051</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F141" s="2">
         <v>2</v>
@@ -7330,19 +7307,19 @@
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="str">
         <f>_xlfn.XLOOKUP(B142, Sheet1!B:B, Sheet1!A:A, "Not Found")</f>
-        <v>IP-026</v>
+        <v>Not Found</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F142" s="2">
         <v>1</v>
@@ -7354,16 +7331,16 @@
         <v>IP-029</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F143" s="2">
         <v>1</v>
@@ -7372,19 +7349,19 @@
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="str">
         <f>_xlfn.XLOOKUP(B144, Sheet1!B:B, Sheet1!A:A, "Not Found")</f>
-        <v>IP-027</v>
+        <v>Not Found</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F144" s="2">
         <v>1</v>
@@ -7396,16 +7373,16 @@
         <v>IP-028</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F145" s="2">
         <v>1</v>
@@ -7414,19 +7391,19 @@
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="str">
         <f>_xlfn.XLOOKUP(B146, Sheet1!B:B, Sheet1!A:A, "Not Found")</f>
-        <v>IP-052</v>
+        <v>Not Found</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F146" s="2">
         <v>1</v>
@@ -7441,13 +7418,13 @@
         <v>31</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E147" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F147" s="2">
         <v>7</v>
@@ -7462,13 +7439,13 @@
         <v>100</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E148" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F148" s="2">
         <v>6</v>
@@ -7480,16 +7457,16 @@
         <v>IP-048</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E149" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F149" s="2">
         <v>8</v>
@@ -7504,13 +7481,13 @@
         <v>68</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E150" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F150" s="2">
         <v>2</v>
@@ -7519,19 +7496,19 @@
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="str">
         <f>_xlfn.XLOOKUP(B151, Sheet1!B:B, Sheet1!A:A, "Not Found")</f>
-        <v>IP-032</v>
+        <v>Not Found</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E151" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F151" s="2">
         <v>2</v>
@@ -7546,13 +7523,13 @@
         <v>73</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E152" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F152" s="2">
         <v>1</v>
@@ -7567,13 +7544,13 @@
         <v>78</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E153" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F153" s="2">
         <v>3</v>
@@ -7585,16 +7562,16 @@
         <v>IP-044</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E154" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F154" s="2">
         <v>1</v>
@@ -7606,16 +7583,16 @@
         <v>IP-053</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E155" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F155" s="2">
         <v>1</v>
@@ -7627,16 +7604,16 @@
         <v>IP-043</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F156" s="2">
         <v>1</v>
@@ -7651,13 +7628,13 @@
         <v>68</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F157" s="2">
         <v>1</v>
@@ -7672,13 +7649,13 @@
         <v>96</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F158" s="2">
         <v>2</v>
@@ -7693,13 +7670,13 @@
         <v>96</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F159" s="2">
         <v>5</v>
@@ -7714,13 +7691,13 @@
         <v>46</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F160" s="2">
         <v>1</v>
@@ -7732,16 +7709,16 @@
         <v>IP-047</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F161" s="2">
         <v>2</v>
@@ -7750,19 +7727,19 @@
     <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="str">
         <f>_xlfn.XLOOKUP(B162, Sheet1!B:B, Sheet1!A:A, "Not Found")</f>
-        <v>IP-032</v>
+        <v>Not Found</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F162" s="2">
         <v>1</v>
@@ -7777,13 +7754,13 @@
         <v>78</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F163" s="2">
         <v>1</v>
@@ -7798,13 +7775,13 @@
         <v>31</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F164" s="2">
         <v>1</v>
@@ -7815,220 +7792,220 @@
     <sortCondition ref="B3:B5"/>
   </sortState>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="87" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="86" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="85" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="84" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="83" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="82" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39">
-    <cfRule type="duplicateValues" dxfId="81" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B40">
-    <cfRule type="duplicateValues" dxfId="80" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41">
-    <cfRule type="duplicateValues" dxfId="79" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="78" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="77" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="75" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="74" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="73" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="72" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="71" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="69" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B50">
-    <cfRule type="duplicateValues" dxfId="67" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="65" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="63" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="61" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="59" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="56" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56">
-    <cfRule type="duplicateValues" dxfId="55" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57">
-    <cfRule type="duplicateValues" dxfId="53" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="51" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="49" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="47" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="45" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="43" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="42" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="40" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="36" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="34" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="31" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="30" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="29" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="27" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="26" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82">
-    <cfRule type="duplicateValues" dxfId="24" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88">
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B98">
-    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99">
-    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119">
-    <cfRule type="duplicateValues" dxfId="16" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="15" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="14" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="13" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B137">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B146">
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B147">
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B151">
-    <cfRule type="duplicateValues" dxfId="9" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B152">
-    <cfRule type="duplicateValues" dxfId="8" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="7" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B161">
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B162">
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B164">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 D161:D1048576 D155 D2:D95 D97:D146" xr:uid="{8270B7E8-CE95-4076-B244-68DB0D08C67D}"/>

--- a/data/Indoor plants.xlsx
+++ b/data/Indoor plants.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480F4E72-767D-4FC1-AF70-593AD41BF7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B233E0-39C5-4F5A-8B4F-EF2CB56FC556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="348">
   <si>
     <t>Plant ID</t>
   </si>
@@ -1075,6 +1075,15 @@
   </si>
   <si>
     <t>Rosa hybrida</t>
+  </si>
+  <si>
+    <t>Portable</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -2420,7 +2429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="9"/>
@@ -2435,7 +2444,7 @@
     <col min="10" max="16384" width="8.90625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="7" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2463,8 +2472,11 @@
       <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" s="7" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J1" s="7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -2493,8 +2505,11 @@
       <c r="I2" s="28" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J2" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>16</v>
       </c>
@@ -2523,8 +2538,11 @@
       <c r="I3" s="28" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J3" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>21</v>
       </c>
@@ -2553,8 +2571,11 @@
       <c r="I4" s="28" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J4" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>26</v>
       </c>
@@ -2583,8 +2604,11 @@
       <c r="I5" s="28" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J5" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>30</v>
       </c>
@@ -2613,8 +2637,11 @@
       <c r="I6" s="28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J6" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>35</v>
       </c>
@@ -2643,8 +2670,11 @@
       <c r="I7" s="28" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J7" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>40</v>
       </c>
@@ -2673,8 +2703,11 @@
       <c r="I8" s="28" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J8" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>45</v>
       </c>
@@ -2703,8 +2736,11 @@
       <c r="I9" s="28" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J9" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>49</v>
       </c>
@@ -2733,8 +2769,11 @@
       <c r="I10" s="28" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J10" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>53</v>
       </c>
@@ -2763,8 +2802,11 @@
       <c r="I11" s="28" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J11" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>58</v>
       </c>
@@ -2793,8 +2835,11 @@
       <c r="I12" s="28" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J12" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>63</v>
       </c>
@@ -2823,8 +2868,11 @@
       <c r="I13" s="28" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J13" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>67</v>
       </c>
@@ -2853,8 +2901,11 @@
       <c r="I14" s="28" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J14" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>72</v>
       </c>
@@ -2883,8 +2934,11 @@
       <c r="I15" s="28" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J15" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>77</v>
       </c>
@@ -2913,8 +2967,11 @@
       <c r="I16" s="28" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J16" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>81</v>
       </c>
@@ -2943,8 +3000,11 @@
       <c r="I17" s="28" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J17" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>85</v>
       </c>
@@ -2973,8 +3033,11 @@
       <c r="I18" s="28" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J18" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>90</v>
       </c>
@@ -3003,8 +3066,11 @@
       <c r="I19" s="28" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J19" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>95</v>
       </c>
@@ -3033,8 +3099,11 @@
       <c r="I20" s="28" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J20" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>99</v>
       </c>
@@ -3063,8 +3132,11 @@
       <c r="I21" s="28" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J21" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>105</v>
       </c>
@@ -3093,8 +3165,11 @@
       <c r="I22" s="28" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J22" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>109</v>
       </c>
@@ -3123,8 +3198,11 @@
       <c r="I23" s="28" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J23" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>112</v>
       </c>
@@ -3153,8 +3231,11 @@
       <c r="I24" s="28" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J24" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>116</v>
       </c>
@@ -3183,8 +3264,11 @@
       <c r="I25" s="28" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J25" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>120</v>
       </c>
@@ -3213,8 +3297,11 @@
       <c r="I26" s="28" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J26" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>124</v>
       </c>
@@ -3243,8 +3330,11 @@
       <c r="I27" s="28" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J27" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>128</v>
       </c>
@@ -3273,8 +3363,11 @@
       <c r="I28" s="28" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J28" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>132</v>
       </c>
@@ -3303,8 +3396,11 @@
       <c r="I29" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J29" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>137</v>
       </c>
@@ -3333,8 +3429,11 @@
       <c r="I30" s="28" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J30" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>141</v>
       </c>
@@ -3363,8 +3462,11 @@
       <c r="I31" s="28" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J31" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>145</v>
       </c>
@@ -3393,8 +3495,11 @@
       <c r="I32" s="28" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J32" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>149</v>
       </c>
@@ -3423,8 +3528,11 @@
       <c r="I33" s="28" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J33" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>152</v>
       </c>
@@ -3453,8 +3561,11 @@
       <c r="I34" s="28" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J34" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>156</v>
       </c>
@@ -3483,8 +3594,11 @@
       <c r="I35" s="28" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J35" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>160</v>
       </c>
@@ -3513,8 +3627,11 @@
       <c r="I36" s="28" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J36" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>165</v>
       </c>
@@ -3543,8 +3660,11 @@
       <c r="I37" s="28" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J37" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>170</v>
       </c>
@@ -3573,8 +3693,11 @@
       <c r="I38" s="28" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J38" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>174</v>
       </c>
@@ -3603,8 +3726,11 @@
       <c r="I39" s="28" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J39" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>179</v>
       </c>
@@ -3633,8 +3759,11 @@
       <c r="I40" s="28" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J40" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>183</v>
       </c>
@@ -3663,8 +3792,11 @@
       <c r="I41" s="28" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J41" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>187</v>
       </c>
@@ -3693,8 +3825,11 @@
       <c r="I42" s="28" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J42" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>191</v>
       </c>
@@ -3723,8 +3858,11 @@
       <c r="I43" s="28" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J43" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>195</v>
       </c>
@@ -3753,8 +3891,11 @@
       <c r="I44" s="28" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J44" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>199</v>
       </c>
@@ -3783,8 +3924,11 @@
       <c r="I45" s="28" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J45" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>203</v>
       </c>
@@ -3813,8 +3957,11 @@
       <c r="I46" s="28" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J46" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>207</v>
       </c>
@@ -3843,8 +3990,11 @@
       <c r="I47" s="28" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J47" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>211</v>
       </c>
@@ -3873,8 +4023,11 @@
       <c r="I48" s="28" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J48" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>215</v>
       </c>
@@ -3903,8 +4056,11 @@
       <c r="I49" s="28" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J49" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>219</v>
       </c>
@@ -3933,8 +4089,11 @@
       <c r="I50" s="28" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J50" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>223</v>
       </c>
@@ -3963,8 +4122,11 @@
       <c r="I51" s="28" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J51" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
         <v>227</v>
       </c>
@@ -3993,8 +4155,11 @@
       <c r="I52" s="28" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J52" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>231</v>
       </c>
@@ -4023,8 +4188,11 @@
       <c r="I53" s="28" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J53" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
         <v>235</v>
       </c>
@@ -4053,8 +4221,11 @@
       <c r="I54" s="28" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J54" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="8"/>
       <c r="B55" s="22"/>
       <c r="C55" s="22"/>
@@ -4062,31 +4233,31 @@
       <c r="E55" s="13"/>
       <c r="H55" s="22"/>
     </row>
-    <row r="56" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="8"/>
     </row>
-    <row r="57" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="8"/>
     </row>
-    <row r="58" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="8"/>
     </row>
-    <row r="59" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="8"/>
     </row>
-    <row r="60" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="8"/>
     </row>
-    <row r="61" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="8"/>
     </row>
-    <row r="62" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="8"/>
     </row>
-    <row r="63" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="8"/>
     </row>
-    <row r="64" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="8"/>
     </row>
     <row r="65" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -4202,11 +4373,14 @@
     <cfRule type="duplicateValues" dxfId="89" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54 B1:B26 B48:B50 B31:B46 B52 B56:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G35 G37:G1048576" xr:uid="{84F914E3-C5A8-4843-B3F4-1A37C7AF587E}">
       <formula1>"Low,Medium,High"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576" xr:uid="{B838D36E-2CB4-403F-A2B2-DECB211C9D66}">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -7792,220 +7966,220 @@
     <sortCondition ref="B3:B5"/>
   </sortState>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="88" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="87" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="86" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="85" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="84" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="83" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39">
-    <cfRule type="duplicateValues" dxfId="82" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B40">
-    <cfRule type="duplicateValues" dxfId="81" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41">
-    <cfRule type="duplicateValues" dxfId="80" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="79" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="78" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="76" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="75" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="74" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="73" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="72" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="70" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B50">
-    <cfRule type="duplicateValues" dxfId="68" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="66" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="64" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="62" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="60" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="57" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56">
-    <cfRule type="duplicateValues" dxfId="56" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57">
-    <cfRule type="duplicateValues" dxfId="54" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="52" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="50" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="48" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="46" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="44" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="41" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="37" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="35" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="34" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="32" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="31" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="30" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="28" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="27" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82">
-    <cfRule type="duplicateValues" dxfId="25" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88">
-    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B98">
-    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99">
-    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="21" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="19" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119">
-    <cfRule type="duplicateValues" dxfId="17" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="16" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="15" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="14" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B137">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B146">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B147">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B151">
-    <cfRule type="duplicateValues" dxfId="10" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B152">
-    <cfRule type="duplicateValues" dxfId="9" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B161">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B162">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B164">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 D161:D1048576 D155 D2:D95 D97:D146" xr:uid="{8270B7E8-CE95-4076-B244-68DB0D08C67D}"/>

--- a/data/Indoor plants.xlsx
+++ b/data/Indoor plants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B233E0-39C5-4F5A-8B4F-EF2CB56FC556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D94703-DCEC-42F3-A62D-0DA45549AA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,9 +87,6 @@
     <t>18-30 ℃</t>
   </si>
   <si>
-    <t>‎https://uob-landscape.github.io/Indoor-plants-pdf/Chinese%20Hibiscus.pdf</t>
-  </si>
-  <si>
     <t>IP-002</t>
   </si>
   <si>
@@ -102,9 +99,6 @@
     <t>18-27 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Philodendron%20hederaceum.pdf</t>
-  </si>
-  <si>
     <t>IP-003</t>
   </si>
   <si>
@@ -117,9 +111,6 @@
     <t>High</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf</t>
-  </si>
-  <si>
     <t>IP-004</t>
   </si>
   <si>
@@ -129,9 +120,6 @@
     <t>https://i.postimg.cc/hQMDYY0h/Arrowhead.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Arrowhead%20Plant.pdf</t>
-  </si>
-  <si>
     <t>IP-005</t>
   </si>
   <si>
@@ -144,9 +132,6 @@
     <t>21-29 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Golden%20Pothos.pdf</t>
-  </si>
-  <si>
     <t>IP-006</t>
   </si>
   <si>
@@ -159,9 +144,6 @@
     <t>18-24 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/satin%20pothos.pdf</t>
-  </si>
-  <si>
     <t>IP-007</t>
   </si>
   <si>
@@ -174,9 +156,6 @@
     <t>16-24 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Araucaria%20heterophylla.pdf</t>
-  </si>
-  <si>
     <t>IP-008</t>
   </si>
   <si>
@@ -186,9 +165,6 @@
     <t>https://i.postimg.cc/TKdmp8sN/Majestic-Palm.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Ravenea%20rivularis.pdf</t>
-  </si>
-  <si>
     <t>IP-009</t>
   </si>
   <si>
@@ -198,9 +174,6 @@
     <t>https://i.postimg.cc/fJ2mFz57/Dwarf-Umbrella-Tree.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Dwarf%20Umbrella%20Tree.pdf</t>
-  </si>
-  <si>
     <t>IP-010</t>
   </si>
   <si>
@@ -213,9 +186,6 @@
     <t>20-27 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Madagascar%20dragon.pdf</t>
-  </si>
-  <si>
     <t>IP-011</t>
   </si>
   <si>
@@ -228,9 +198,6 @@
     <t>18-29 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Rainbow%20Tree.pdf</t>
-  </si>
-  <si>
     <t>IP-012</t>
   </si>
   <si>
@@ -240,9 +207,6 @@
     <t>https://i.postimg.cc/Yj76LyhF/cylindrical-snake-plant.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Cylindrical%20Snake%20Plant.pdf</t>
-  </si>
-  <si>
     <t>IP-013</t>
   </si>
   <si>
@@ -255,9 +219,6 @@
     <t>16-26 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Money%20tree.pdf</t>
-  </si>
-  <si>
     <t>IP-014</t>
   </si>
   <si>
@@ -270,9 +231,6 @@
     <t>18-25 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Ficus%20elastica%20-%20W.pdf</t>
-  </si>
-  <si>
     <t>IP-015</t>
   </si>
   <si>
@@ -282,9 +240,6 @@
     <t>https://i.postimg.cc/fVyjTtkg/Codiaeum-variegatum-Garden-croton.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Codiaeum%20variegatum.pdf</t>
-  </si>
-  <si>
     <t>IP-016</t>
   </si>
   <si>
@@ -294,9 +249,6 @@
     <t>https://i.postimg.cc/rDDx2BYB/Ficus-microcarpa.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Ficus%20microcarpa.pdf</t>
-  </si>
-  <si>
     <t>IP-017</t>
   </si>
   <si>
@@ -309,9 +261,6 @@
     <t>18-26 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Kalanchoe%20blossfeldiana%202.pdf</t>
-  </si>
-  <si>
     <t>IP-018</t>
   </si>
   <si>
@@ -324,9 +273,6 @@
     <t>20-30 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Paper%20flower.pdf</t>
-  </si>
-  <si>
     <t>IP-019</t>
   </si>
   <si>
@@ -336,9 +282,6 @@
     <t>https://i.postimg.cc/yg4FPLjw/Corn-Plant.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Corn%20Plant.pdf</t>
-  </si>
-  <si>
     <t>IP-020</t>
   </si>
   <si>
@@ -354,9 +297,6 @@
     <t>18-28 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Zanzibar%20Gem%2022.pdf</t>
-  </si>
-  <si>
     <t>IP-021</t>
   </si>
   <si>
@@ -366,18 +306,12 @@
     <t>https://i.postimg.cc/75j7HKFf/English-lavender.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/‎English%20Lavender.pdf</t>
-  </si>
-  <si>
     <t>IP-022</t>
   </si>
   <si>
     <t>https://i.postimg.cc/WhP0cqwv/LEMON-GRASS.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Lemon%20grass.pdf</t>
-  </si>
-  <si>
     <t>IP-023</t>
   </si>
   <si>
@@ -387,9 +321,6 @@
     <t>https://i.postimg.cc/bDD1pQ5z/Horse-mint.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Horse%20Mint.pdf</t>
-  </si>
-  <si>
     <t>IP-024</t>
   </si>
   <si>
@@ -399,9 +330,6 @@
     <t>https://i.postimg.cc/VS5CWqmj/Mexican-mint.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Mexican%20Mint.pdf</t>
-  </si>
-  <si>
     <t>IP-025</t>
   </si>
   <si>
@@ -411,9 +339,6 @@
     <t>https://i.postimg.cc/gx7ywzZc/common-sage.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Common%20sage.pdf</t>
-  </si>
-  <si>
     <t>IP-026</t>
   </si>
   <si>
@@ -423,9 +348,6 @@
     <t>https://i.postimg.cc/8FrRM2RR/Thymus.avif</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Thymus%20vulgaris.pdf</t>
-  </si>
-  <si>
     <t>IP-027</t>
   </si>
   <si>
@@ -435,9 +357,6 @@
     <t>https://i.postimg.cc/w357JfLC/spearmint.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Mentha%20spicata.pdf</t>
-  </si>
-  <si>
     <t>IP-028</t>
   </si>
   <si>
@@ -450,9 +369,6 @@
     <t>15-21 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Salvia%20rosmarinus.pdf</t>
-  </si>
-  <si>
     <t>IP-029</t>
   </si>
   <si>
@@ -462,9 +378,6 @@
     <t>https://i.postimg.cc/Mf0Mptm8/pelargonium.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Pelargonium.pdf</t>
-  </si>
-  <si>
     <t>IP-030</t>
   </si>
   <si>
@@ -474,9 +387,6 @@
     <t>https://i.postimg.cc/8FWvjhGw/Flame-of-the-woods.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Flame%20of%20the%20woods.pdf</t>
-  </si>
-  <si>
     <t>IP-031</t>
   </si>
   <si>
@@ -486,18 +396,12 @@
     <t>https://i.postimg.cc/Z9yqqVJD/WEEPING-FIG.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Weeping%20Fig.pdf</t>
-  </si>
-  <si>
     <t>IP-032</t>
   </si>
   <si>
     <t>https://i.postimg.cc/G8wmTG23/Yellow-butterfly-palm.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/‎Yellow%20Butterfly%20Palm.pdf</t>
-  </si>
-  <si>
     <t>IP-033</t>
   </si>
   <si>
@@ -507,9 +411,6 @@
     <t>https://i.postimg.cc/n9f9xN7k/Peace-lily.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/‎Peace%20lily.pdf</t>
-  </si>
-  <si>
     <t>IP-034</t>
   </si>
   <si>
@@ -519,9 +420,6 @@
     <t>https://i.postimg.cc/1nQq6f5S/Flamingo-Flower.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/‎Flamingo%20flower.pdf</t>
-  </si>
-  <si>
     <t>IP-035</t>
   </si>
   <si>
@@ -534,9 +432,6 @@
     <t>18-35 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/‎⁨Lucky%20Bamboo.pdf</t>
-  </si>
-  <si>
     <t>IP-036</t>
   </si>
   <si>
@@ -549,9 +444,6 @@
     <t>15-30 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Snake%20plant-%20Sansevieria%20trifasciata.pdf</t>
-  </si>
-  <si>
     <t>IP-037</t>
   </si>
   <si>
@@ -561,9 +453,6 @@
     <t>https://i.postimg.cc/3dCm8rtD/Madagascar-periwinkle.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Madagascar%20periwinkle.pdf</t>
-  </si>
-  <si>
     <t>IP-038</t>
   </si>
   <si>
@@ -576,9 +465,6 @@
     <t>15-25 ℃</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/silver%20squill.pdf</t>
-  </si>
-  <si>
     <t>IP-039</t>
   </si>
   <si>
@@ -588,9 +474,6 @@
     <t>https://i.postimg.cc/fJTYBt7T/Dieffenbachia.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Dieffenbachia%20seguine.pdf</t>
-  </si>
-  <si>
     <t>IP-040</t>
   </si>
   <si>
@@ -600,9 +483,6 @@
     <t>https://i.postimg.cc/mtbyJ644/Chinees-evergreen.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Chinese%20Evergreen.pdf</t>
-  </si>
-  <si>
     <t>IP-041</t>
   </si>
   <si>
@@ -612,9 +492,6 @@
     <t>https://i.postimg.cc/bd12gNcF/Philodendron-Xanadu.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Philodendron%20Xanadu.pdf</t>
-  </si>
-  <si>
     <t>IP-042</t>
   </si>
   <si>
@@ -624,9 +501,6 @@
     <t>https://i.postimg.cc/sMxXk3qz/Tradescantia-spathacea.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Tradescantia%20spathacea.pdf</t>
-  </si>
-  <si>
     <t>IP-043</t>
   </si>
   <si>
@@ -636,9 +510,6 @@
     <t>https://i.postimg.cc/5Xr01ZWC/Variegated-Snake-Plant.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Variegatef%20snake%20plant-%20Sansevieria%20trifasciata%20var.%20laurentii.pdf</t>
-  </si>
-  <si>
     <t>IP-044</t>
   </si>
   <si>
@@ -648,9 +519,6 @@
     <t>https://i.postimg.cc/GHrT5wb3/Ponytail-Palm.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Ponytail%20Palm.pdf</t>
-  </si>
-  <si>
     <t>IP-045</t>
   </si>
   <si>
@@ -660,9 +528,6 @@
     <t>https://i.postimg.cc/dL43NhWn/Spider-Plant.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Spider%20plant.pdf</t>
-  </si>
-  <si>
     <t>IP-046</t>
   </si>
   <si>
@@ -672,9 +537,6 @@
     <t>https://i.postimg.cc/xX1J9vkW/Purple-Heart.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Perple%20heart.pdf</t>
-  </si>
-  <si>
     <t>IP-047</t>
   </si>
   <si>
@@ -684,9 +546,6 @@
     <t>https://i.postimg.cc/vD7vPwpX/Cambodian-Dragon-Tree.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Dracaena_cambodiana%20-%20W.pdf</t>
-  </si>
-  <si>
     <t>IP-048</t>
   </si>
   <si>
@@ -696,9 +555,6 @@
     <t>https://i.postimg.cc/HjtQw4yh/Dracaena-reflexa-song-of-india.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Dracaena%20reflexa (%20song%20of%20india).pdf</t>
-  </si>
-  <si>
     <t>IP-049</t>
   </si>
   <si>
@@ -708,9 +564,6 @@
     <t>https://i.postimg.cc/ZvJ6k01H/cycas-revoluta-sago-plam.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Sago%20Palm.pdf</t>
-  </si>
-  <si>
     <t>IP-050</t>
   </si>
   <si>
@@ -720,9 +573,6 @@
     <t>https://i.postimg.cc/ry32bMjD/Portulaca-umbraticola.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/portulaca%20umbraticola.pdf</t>
-  </si>
-  <si>
     <t>IP-051</t>
   </si>
   <si>
@@ -732,9 +582,6 @@
     <t>https://i.postimg.cc/JzwNkSV2/Portulaca-grandiflora.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Portulaca%20grandiflora.pdf</t>
-  </si>
-  <si>
     <t>IP-052</t>
   </si>
   <si>
@@ -744,9 +591,6 @@
     <t>https://i.postimg.cc/svV1JYJv/Tea-rose.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Rosa%20hybrids.pdf</t>
-  </si>
-  <si>
     <t>IP-053</t>
   </si>
   <si>
@@ -756,9 +600,6 @@
     <t>https://i.postimg.cc/QVZbkdnH/Brazilian-Joyweed.jpg</t>
   </si>
   <si>
-    <t>https://uob-landscape.github.io/Indoor-plants-pdf/Brazilian%20Joyweed.pdf</t>
-  </si>
-  <si>
     <t>Location type</t>
   </si>
   <si>
@@ -1084,6 +925,165 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/‎Chinese Hibiscus.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Pelargonium.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Crown of Thorns.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Arrowhead Plant.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Philodendron hederaceum.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Golden Pothos.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/satin pothos.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Araucaria heterophylla.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Ravenea rivularis.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Dwarf Umbrella Tree.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Madagascar dragon.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Rainbow Tree.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Cylindrical Snake Plant.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Money tree.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Ficus elastica - W.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Codiaeum variegatum.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Ficus microcarpa.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Kalanchoe blossfeldiana 2.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Paper flower.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Corn Plant.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Zanzibar Gem 22.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/‎English Lavender.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Lemon grass.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Horse Mint.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Mexican Mint.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Common sage.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Thymus vulgaris.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Mentha spicata.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Salvia rosmarinus.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Flame of the woods.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Weeping Fig.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/‎Yellow Butterfly Palm.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/‎Peace lily.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/‎Flamingo flower.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Snake plant- Sansevieria trifasciata.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Madagascar periwinkle.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/silver squill.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Dieffenbachia seguine.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Chinese Evergreen.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Philodendron Xanadu.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Tradescantia spathacea.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Variegatef snake plant- Sansevieria trifasciata var. laurentii.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Ponytail Palm.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Spider plant.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Perple heart.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Dracaena_cambodiana - W.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Dracaena reflexa ( song of india).pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Sago Palm.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/portulaca umbraticola.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Portulaca grandiflora.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Rosa hybrids.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/Brazilian Joyweed.pdf</t>
+  </si>
+  <si>
+    <t>https://uob-landscape.github.io/PDF-files/‎‎⁨Lucky Bamboo.pdf</t>
   </si>
 </sst>
 </file>
@@ -2473,7 +2473,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>345</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="7" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2484,7 +2484,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>285</v>
+        <v>232</v>
       </c>
       <c r="D2" s="10" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Chinese%20Hibiscus.jpg", "Open Image")</f>
@@ -2503,28 +2503,28 @@
         <v>14</v>
       </c>
       <c r="I2" s="28" t="s">
-        <v>15</v>
+        <v>295</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>17</v>
-      </c>
       <c r="C3" s="9" t="s">
-        <v>286</v>
+        <v>233</v>
       </c>
       <c r="D3" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/heartleaf.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>12</v>
@@ -2533,64 +2533,64 @@
         <v>13</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>20</v>
+        <v>299</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>287</v>
+        <v>234</v>
       </c>
       <c r="D4" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/crown%20of%20thorns.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>25</v>
+        <v>297</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>288</v>
+        <v>235</v>
       </c>
       <c r="D5" s="17" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Arrowhead.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>12</v>
@@ -2599,31 +2599,31 @@
         <v>13</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>29</v>
+        <v>298</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>289</v>
+        <v>236</v>
       </c>
       <c r="D6" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/golden%20phothos.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>12</v>
@@ -2632,31 +2632,31 @@
         <v>13</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>34</v>
+        <v>300</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>347</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>290</v>
+        <v>237</v>
       </c>
       <c r="D7" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Satin%20pothos.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>12</v>
@@ -2665,31 +2665,31 @@
         <v>13</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>39</v>
+        <v>301</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>291</v>
+        <v>238</v>
       </c>
       <c r="D8" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Araucaria%20heterophylla-Norfolk%20Island%20pine.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>12</v>
@@ -2698,31 +2698,31 @@
         <v>13</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>44</v>
+        <v>302</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="D9" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Majestic%20Palm.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>12</v>
@@ -2731,64 +2731,64 @@
         <v>13</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I9" s="28" t="s">
-        <v>48</v>
+        <v>303</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>293</v>
+        <v>240</v>
       </c>
       <c r="D10" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Chinees%20evergreen.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I10" s="28" t="s">
-        <v>52</v>
+        <v>304</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>294</v>
+        <v>241</v>
       </c>
       <c r="D11" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Madagascar%20dragon%20tree.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>12</v>
@@ -2797,97 +2797,97 @@
         <v>13</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>57</v>
+        <v>305</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="D12" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/rainbow%20tree.jpg","Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>62</v>
+        <v>306</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>296</v>
+        <v>243</v>
       </c>
       <c r="D13" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/cylindrical%20snake%20plant.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>66</v>
+        <v>307</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>297</v>
+        <v>244</v>
       </c>
       <c r="D14" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Money%20tree.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>12</v>
@@ -2896,31 +2896,31 @@
         <v>13</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>71</v>
+        <v>308</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="D15" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Rubber%20tree-Ficus%20elastica.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>12</v>
@@ -2929,163 +2929,163 @@
         <v>13</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>76</v>
+        <v>309</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="D16" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Codiaeum%20variegatum-Garden%20croton.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I16" s="28" t="s">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="D17" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Ficus%20microcarpa.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I17" s="28" t="s">
-        <v>84</v>
+        <v>311</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="D18" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Kalanchoe%20blossfeldiana.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>89</v>
+        <v>312</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="D19" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Paper%20flower.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="I19" s="28" t="s">
-        <v>94</v>
+        <v>313</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>303</v>
+        <v>250</v>
       </c>
       <c r="D20" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Corn%20Plant.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>12</v>
@@ -3094,625 +3094,625 @@
         <v>13</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I20" s="28" t="s">
-        <v>98</v>
+        <v>314</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>304</v>
+        <v>251</v>
       </c>
       <c r="D21" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Zanzibar%20Gem%20(2).jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I21" s="28" t="s">
-        <v>104</v>
+        <v>315</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>347</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="D22" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/English%20lavender.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I22" s="28" t="s">
-        <v>108</v>
+        <v>316</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>306</v>
+        <v>253</v>
       </c>
       <c r="D23" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/LEMON%20GRASS.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="I23" s="28" t="s">
-        <v>111</v>
+        <v>317</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>307</v>
+        <v>254</v>
       </c>
       <c r="D24" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Horse%20mint.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I24" s="28" t="s">
-        <v>115</v>
+        <v>318</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c r="D25" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Mexican%20mint.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I25" s="28" t="s">
-        <v>119</v>
+        <v>319</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>309</v>
+        <v>256</v>
       </c>
       <c r="D26" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/common%20sage.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="I26" s="28" t="s">
-        <v>123</v>
+        <v>320</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>340</v>
+        <v>287</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="D27" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/thymus.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>127</v>
+        <v>321</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>341</v>
+        <v>288</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>311</v>
+        <v>258</v>
       </c>
       <c r="D28" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/spearmint.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>131</v>
+        <v>322</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>347</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>312</v>
+        <v>259</v>
       </c>
       <c r="D29" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Rose%20mary.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="I29" s="28" t="s">
-        <v>136</v>
+        <v>323</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>313</v>
+        <v>260</v>
       </c>
       <c r="D30" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/pelargonium.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I30" s="28" t="s">
-        <v>140</v>
+        <v>296</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>314</v>
+        <v>261</v>
       </c>
       <c r="D31" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Flame%20of%20the%20woods.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="I31" s="28" t="s">
-        <v>144</v>
+        <v>324</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>347</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>315</v>
+        <v>262</v>
       </c>
       <c r="D32" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/WEEPING%20FIG.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I32" s="28" t="s">
-        <v>148</v>
+        <v>325</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>342</v>
+        <v>289</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>316</v>
+        <v>263</v>
       </c>
       <c r="D33" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Yellow%20butterfly%20palm.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I33" s="28" t="s">
-        <v>151</v>
+        <v>326</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="D34" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Peace%20lily.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I34" s="28" t="s">
-        <v>155</v>
+        <v>327</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>343</v>
+        <v>290</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="D35" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Flamingo%20Flower.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I35" s="28" t="s">
-        <v>159</v>
+        <v>328</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="D36" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Lucky%20Bamboo.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="I36" s="28" t="s">
-        <v>164</v>
+        <v>347</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>320</v>
+        <v>267</v>
       </c>
       <c r="D37" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Snake%20plant.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="I37" s="28" t="s">
-        <v>169</v>
+        <v>329</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="D38" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Madagascar%20dragon%20tree.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="F38" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="I38" s="28" t="s">
-        <v>173</v>
+        <v>330</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="D39" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Silver%20squill.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>12</v>
@@ -3721,31 +3721,31 @@
         <v>13</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="I39" s="28" t="s">
-        <v>178</v>
+        <v>331</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>323</v>
+        <v>270</v>
       </c>
       <c r="D40" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Dieffenbachia.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>12</v>
@@ -3754,31 +3754,31 @@
         <v>13</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I40" s="28" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="D41" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Chinees%20evergreen.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>12</v>
@@ -3787,31 +3787,31 @@
         <v>13</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I41" s="28" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="D42" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Philodendron%20Xanadu.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>12</v>
@@ -3820,31 +3820,31 @@
         <v>13</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I42" s="28" t="s">
-        <v>190</v>
+        <v>334</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="D43" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Tradescantia%20spathacea.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>12</v>
@@ -3853,31 +3853,31 @@
         <v>13</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I43" s="28" t="s">
-        <v>194</v>
+        <v>335</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="D44" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Variegated%20Snake%20Plant.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>197</v>
+        <v>155</v>
       </c>
       <c r="F44" s="12" t="s">
         <v>12</v>
@@ -3889,28 +3889,28 @@
         <v>14</v>
       </c>
       <c r="I44" s="28" t="s">
-        <v>198</v>
+        <v>336</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="D45" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Ponytail%20Palm.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>12</v>
@@ -3919,31 +3919,31 @@
         <v>13</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I45" s="28" t="s">
-        <v>202</v>
+        <v>337</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="D46" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Spider%20Plant.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>12</v>
@@ -3952,31 +3952,31 @@
         <v>13</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I46" s="28" t="s">
-        <v>206</v>
+        <v>338</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="D47" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Purple%20Heart.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>12</v>
@@ -3988,28 +3988,28 @@
         <v>14</v>
       </c>
       <c r="I47" s="28" t="s">
-        <v>210</v>
+        <v>339</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>347</v>
+        <v>294</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>331</v>
+        <v>278</v>
       </c>
       <c r="D48" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Cambodian%20Dragon%20Tree.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>12</v>
@@ -4018,31 +4018,31 @@
         <v>13</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="I48" s="28" t="s">
-        <v>214</v>
+        <v>340</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>332</v>
+        <v>279</v>
       </c>
       <c r="D49" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Dracaena%20reflexa%20(%20song%20of%20india).jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>12</v>
@@ -4051,31 +4051,31 @@
         <v>13</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I49" s="28" t="s">
-        <v>218</v>
+        <v>341</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
-        <v>219</v>
+        <v>171</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>220</v>
+        <v>172</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="D50" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/cycas%20revoluta%20(sago%20plam).jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>221</v>
+        <v>173</v>
       </c>
       <c r="F50" s="12" t="s">
         <v>12</v>
@@ -4084,130 +4084,130 @@
         <v>13</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I50" s="28" t="s">
-        <v>222</v>
+        <v>342</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
-        <v>223</v>
+        <v>174</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>224</v>
+        <v>175</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>334</v>
+        <v>281</v>
       </c>
       <c r="D51" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/%E2%80%8FPortulaca%20umbraticola.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H51" s="21" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="I51" s="28" t="s">
-        <v>226</v>
+        <v>343</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>347</v>
+        <v>294</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="D52" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Portulaca%20grandiflora.jpg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>229</v>
+        <v>179</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="I52" s="28" t="s">
-        <v>230</v>
+        <v>344</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>344</v>
+        <v>291</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="D53" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Tea%20rose.jpeg", "Open Image")</f>
         <v>Open Image</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="I53" s="28" t="s">
-        <v>234</v>
+        <v>345</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
-        <v>235</v>
+        <v>183</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="D54" s="13" t="str">
         <f>HYPERLINK("https://stuuobedu-my.sharepoint.com/personal/landscape_uob_edu_bh/Documents/Indoor%20plants/Images/Brazilian%20Joyweed.jpeg","Open Image ")</f>
         <v xml:space="preserve">Open Image </v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>237</v>
+        <v>185</v>
       </c>
       <c r="F54" s="12" t="s">
         <v>12</v>
@@ -4216,13 +4216,13 @@
         <v>13</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="I54" s="28" t="s">
-        <v>238</v>
+        <v>346</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
@@ -4438,65 +4438,65 @@
     <hyperlink ref="E54" r:id="rId52" xr:uid="{3F6FFD0C-1482-427F-B42C-90EE37526E34}"/>
     <hyperlink ref="E51" r:id="rId53" xr:uid="{2AABB419-20C6-4B83-9000-0AABA2A4BD8D}"/>
     <hyperlink ref="I2" r:id="rId54" xr:uid="{FDE2AFCB-B7BB-4F61-A365-E50A4912FA66}"/>
-    <hyperlink ref="I3" r:id="rId55" xr:uid="{A4EB3D9D-D492-451E-A3A4-4A344DF2725A}"/>
+    <hyperlink ref="I3" r:id="rId55" display="https://uob-landscape.github.io/PDF-files/Philodendron%20hederaceum.pdf" xr:uid="{A4EB3D9D-D492-451E-A3A4-4A344DF2725A}"/>
     <hyperlink ref="I4" r:id="rId56" xr:uid="{25746F2F-51B4-45AD-BD6D-61F6233B924B}"/>
     <hyperlink ref="I5:I7" r:id="rId57" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{EF828A93-4AAA-4C76-9FEA-A4E5B9F45BD1}"/>
-    <hyperlink ref="I5" r:id="rId58" xr:uid="{F8E4F2FF-1D44-4D69-9803-4650A607B7B2}"/>
-    <hyperlink ref="I6" r:id="rId59" xr:uid="{7F12CE4C-D7D2-4350-95E1-DE2449CA7ED7}"/>
-    <hyperlink ref="I7:I19" r:id="rId60" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{F30A200C-D6F1-4028-91A9-F2F186EACAA3}"/>
-    <hyperlink ref="I20:I21" r:id="rId61" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{8A5AD55D-643B-4303-A2F2-A26F17C06CCB}"/>
-    <hyperlink ref="I34:I35" r:id="rId62" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{7ED6486D-35D7-4EB0-BE76-112251533852}"/>
-    <hyperlink ref="I48:I49" r:id="rId63" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{A9AC54E6-B715-4C13-B9AF-D2D6839991C0}"/>
-    <hyperlink ref="I20" r:id="rId64" xr:uid="{C474CB30-9342-4935-A1CF-8D2629EFA719}"/>
-    <hyperlink ref="I34" r:id="rId65" xr:uid="{8E8A0AAA-08E2-4ACB-9867-F454B9B564ED}"/>
-    <hyperlink ref="I48" r:id="rId66" xr:uid="{A52A6E9D-5BBB-46B1-81F3-37AF4B92D644}"/>
-    <hyperlink ref="I21:I33" r:id="rId67" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{3934B3E9-C8D2-4E98-9022-3D7333F4530E}"/>
-    <hyperlink ref="I35:I47" r:id="rId68" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{8BC8C650-E65A-4224-8FCB-24827633C67B}"/>
-    <hyperlink ref="I7" r:id="rId69" xr:uid="{C94AF80F-D188-43D7-8D2C-23464CFC14AB}"/>
-    <hyperlink ref="I8" r:id="rId70" xr:uid="{5DCF9DD9-000C-4C34-8BC0-E9D5F4E7341B}"/>
-    <hyperlink ref="I9" r:id="rId71" xr:uid="{048A6F1E-5EE4-4DDB-ADBF-1558FE134109}"/>
-    <hyperlink ref="I10" r:id="rId72" xr:uid="{EBAAC964-EA14-4E38-8614-AC3953F3F304}"/>
-    <hyperlink ref="I11" r:id="rId73" xr:uid="{86C3B087-145F-4220-A59D-B42A782FF2BB}"/>
-    <hyperlink ref="I12" r:id="rId74" xr:uid="{C66FB600-8C22-49C3-A1AC-ED4BB8A63F24}"/>
-    <hyperlink ref="I13" r:id="rId75" xr:uid="{CB0EB354-34BC-4C1D-943D-EBDCC4832973}"/>
-    <hyperlink ref="I14" r:id="rId76" xr:uid="{5E4BABAC-31BC-41EF-9D21-1146FC213E4D}"/>
-    <hyperlink ref="I15" r:id="rId77" xr:uid="{2FC2ECA6-E2BB-460A-99F1-33203677C7A7}"/>
-    <hyperlink ref="I16" r:id="rId78" xr:uid="{791D1633-FFA6-4414-9218-F7C213DDABAC}"/>
-    <hyperlink ref="I17" r:id="rId79" xr:uid="{C7A625F7-CC73-4754-B405-A7C74339ADEF}"/>
-    <hyperlink ref="I18" r:id="rId80" xr:uid="{A4CAE196-BC41-466B-88F9-E6A6D63733C6}"/>
-    <hyperlink ref="I19" r:id="rId81" xr:uid="{2CE13348-A7E4-489C-BFE9-6734F82D3FFA}"/>
-    <hyperlink ref="I21" r:id="rId82" xr:uid="{855F1622-495E-4193-9447-E4CF99C2D901}"/>
-    <hyperlink ref="I22" r:id="rId83" xr:uid="{46AD3465-42C2-44D1-AB73-221DE0A1AAFF}"/>
-    <hyperlink ref="I23" r:id="rId84" xr:uid="{64E455FE-890B-4FAC-B518-913FB45E97F2}"/>
-    <hyperlink ref="I24" r:id="rId85" xr:uid="{17222DD6-C905-4E09-AF92-4E60705792E9}"/>
-    <hyperlink ref="I25" r:id="rId86" xr:uid="{55B6BEF0-8473-495B-973E-9CF6B125E8FB}"/>
-    <hyperlink ref="I26" r:id="rId87" xr:uid="{3C7E5A51-22C2-4BC9-97D8-5C3647AE71AD}"/>
-    <hyperlink ref="I27" r:id="rId88" xr:uid="{AF6F1F42-27A4-46E8-AA29-37F671EFADA8}"/>
-    <hyperlink ref="I28" r:id="rId89" xr:uid="{4B082801-6244-4D32-BD1B-99F081E97698}"/>
-    <hyperlink ref="I29" r:id="rId90" xr:uid="{C9F28684-AD23-42A5-BBF7-D86ACAB007EB}"/>
-    <hyperlink ref="I30" r:id="rId91" xr:uid="{87514782-4D76-40E5-9B8D-60C8FE970C18}"/>
-    <hyperlink ref="I31" r:id="rId92" xr:uid="{6BB672C7-6611-4E2A-8DCB-4A12C199FA23}"/>
-    <hyperlink ref="I32" r:id="rId93" xr:uid="{E86FCFB9-5608-4850-A5ED-A67330838BBD}"/>
-    <hyperlink ref="I33" r:id="rId94" xr:uid="{24847E9B-EC3B-4706-B5D7-E96299D8FCE7}"/>
-    <hyperlink ref="I35" r:id="rId95" xr:uid="{5D875E55-FA05-42F5-9624-D365B9FCF580}"/>
-    <hyperlink ref="I36" r:id="rId96" xr:uid="{BC52199B-D637-4949-B7E2-EE16E5CCF544}"/>
-    <hyperlink ref="I37" r:id="rId97" xr:uid="{E285E0E1-E10F-4573-8B5D-14393F2018FF}"/>
-    <hyperlink ref="I38" r:id="rId98" xr:uid="{3E7CA2F9-EE2D-43F1-9F9C-30E7DB42ECF5}"/>
-    <hyperlink ref="I39" r:id="rId99" xr:uid="{928AC6DA-16BB-4AF8-8DB1-9ED23834C460}"/>
-    <hyperlink ref="I40" r:id="rId100" xr:uid="{E536F454-463E-4283-B208-0F490A944082}"/>
-    <hyperlink ref="I41" r:id="rId101" xr:uid="{850B09B6-55C1-4798-906D-B273A1D81D5C}"/>
-    <hyperlink ref="I42" r:id="rId102" xr:uid="{3CB74BBF-4D3F-4BC1-96C4-ADF57D2DE694}"/>
-    <hyperlink ref="I43" r:id="rId103" xr:uid="{12FE35A1-E3EB-4149-A6AF-D5686FDB1D00}"/>
-    <hyperlink ref="I44" r:id="rId104" xr:uid="{E1D776BB-59E6-4EDD-9DE7-DF885C654024}"/>
-    <hyperlink ref="I45" r:id="rId105" xr:uid="{3FCCCC27-14FE-489A-BA41-BE93FAB29F18}"/>
-    <hyperlink ref="I46" r:id="rId106" xr:uid="{E1A118C9-2C49-485A-8CFD-68FA8DF10434}"/>
-    <hyperlink ref="I47" r:id="rId107" xr:uid="{6BA16956-09AD-4E19-A6B3-3865374CA990}"/>
-    <hyperlink ref="I49" r:id="rId108" xr:uid="{83BE5218-6875-49A8-956E-1D08C7D5D1FA}"/>
-    <hyperlink ref="I50" r:id="rId109" xr:uid="{79738EA3-AAF9-4607-9485-79FB032A5B93}"/>
-    <hyperlink ref="I51" r:id="rId110" xr:uid="{16B23793-DE5C-40D5-8508-81CB751A116B}"/>
-    <hyperlink ref="I52" r:id="rId111" xr:uid="{B45AC07C-6967-40DF-AA68-11D16638538C}"/>
-    <hyperlink ref="I53" r:id="rId112" xr:uid="{029EB02F-755A-41DD-8B1B-9F81260CB5B3}"/>
-    <hyperlink ref="I54" r:id="rId113" xr:uid="{EEFDDD39-4424-4F94-88FF-8697250AA9D7}"/>
+    <hyperlink ref="I6" r:id="rId58" xr:uid="{7F12CE4C-D7D2-4350-95E1-DE2449CA7ED7}"/>
+    <hyperlink ref="I7:I19" r:id="rId59" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{F30A200C-D6F1-4028-91A9-F2F186EACAA3}"/>
+    <hyperlink ref="I20:I21" r:id="rId60" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{8A5AD55D-643B-4303-A2F2-A26F17C06CCB}"/>
+    <hyperlink ref="I34:I35" r:id="rId61" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{7ED6486D-35D7-4EB0-BE76-112251533852}"/>
+    <hyperlink ref="I48:I49" r:id="rId62" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{A9AC54E6-B715-4C13-B9AF-D2D6839991C0}"/>
+    <hyperlink ref="I20" r:id="rId63" xr:uid="{C474CB30-9342-4935-A1CF-8D2629EFA719}"/>
+    <hyperlink ref="I34" r:id="rId64" xr:uid="{8E8A0AAA-08E2-4ACB-9867-F454B9B564ED}"/>
+    <hyperlink ref="I48" r:id="rId65" xr:uid="{A52A6E9D-5BBB-46B1-81F3-37AF4B92D644}"/>
+    <hyperlink ref="I21:I33" r:id="rId66" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{3934B3E9-C8D2-4E98-9022-3D7333F4530E}"/>
+    <hyperlink ref="I35:I47" r:id="rId67" display="https://uob-landscape.github.io/Indoor-plants-pdf/Crown%20of%20Thorns.pdf" xr:uid="{8BC8C650-E65A-4224-8FCB-24827633C67B}"/>
+    <hyperlink ref="I7" r:id="rId68" xr:uid="{C94AF80F-D188-43D7-8D2C-23464CFC14AB}"/>
+    <hyperlink ref="I8" r:id="rId69" xr:uid="{5DCF9DD9-000C-4C34-8BC0-E9D5F4E7341B}"/>
+    <hyperlink ref="I9" r:id="rId70" xr:uid="{048A6F1E-5EE4-4DDB-ADBF-1558FE134109}"/>
+    <hyperlink ref="I10" r:id="rId71" xr:uid="{EBAAC964-EA14-4E38-8614-AC3953F3F304}"/>
+    <hyperlink ref="I11" r:id="rId72" xr:uid="{86C3B087-145F-4220-A59D-B42A782FF2BB}"/>
+    <hyperlink ref="I12" r:id="rId73" xr:uid="{C66FB600-8C22-49C3-A1AC-ED4BB8A63F24}"/>
+    <hyperlink ref="I13" r:id="rId74" xr:uid="{CB0EB354-34BC-4C1D-943D-EBDCC4832973}"/>
+    <hyperlink ref="I14" r:id="rId75" xr:uid="{5E4BABAC-31BC-41EF-9D21-1146FC213E4D}"/>
+    <hyperlink ref="I15" r:id="rId76" xr:uid="{2FC2ECA6-E2BB-460A-99F1-33203677C7A7}"/>
+    <hyperlink ref="I16" r:id="rId77" xr:uid="{791D1633-FFA6-4414-9218-F7C213DDABAC}"/>
+    <hyperlink ref="I17" r:id="rId78" xr:uid="{C7A625F7-CC73-4754-B405-A7C74339ADEF}"/>
+    <hyperlink ref="I18" r:id="rId79" xr:uid="{A4CAE196-BC41-466B-88F9-E6A6D63733C6}"/>
+    <hyperlink ref="I19" r:id="rId80" xr:uid="{2CE13348-A7E4-489C-BFE9-6734F82D3FFA}"/>
+    <hyperlink ref="I21" r:id="rId81" xr:uid="{855F1622-495E-4193-9447-E4CF99C2D901}"/>
+    <hyperlink ref="I22" r:id="rId82" xr:uid="{46AD3465-42C2-44D1-AB73-221DE0A1AAFF}"/>
+    <hyperlink ref="I23" r:id="rId83" xr:uid="{64E455FE-890B-4FAC-B518-913FB45E97F2}"/>
+    <hyperlink ref="I24" r:id="rId84" xr:uid="{17222DD6-C905-4E09-AF92-4E60705792E9}"/>
+    <hyperlink ref="I25" r:id="rId85" xr:uid="{55B6BEF0-8473-495B-973E-9CF6B125E8FB}"/>
+    <hyperlink ref="I26" r:id="rId86" xr:uid="{3C7E5A51-22C2-4BC9-97D8-5C3647AE71AD}"/>
+    <hyperlink ref="I27" r:id="rId87" xr:uid="{AF6F1F42-27A4-46E8-AA29-37F671EFADA8}"/>
+    <hyperlink ref="I28" r:id="rId88" xr:uid="{4B082801-6244-4D32-BD1B-99F081E97698}"/>
+    <hyperlink ref="I29" r:id="rId89" xr:uid="{C9F28684-AD23-42A5-BBF7-D86ACAB007EB}"/>
+    <hyperlink ref="I30" r:id="rId90" xr:uid="{87514782-4D76-40E5-9B8D-60C8FE970C18}"/>
+    <hyperlink ref="I31" r:id="rId91" xr:uid="{6BB672C7-6611-4E2A-8DCB-4A12C199FA23}"/>
+    <hyperlink ref="I32" r:id="rId92" xr:uid="{E86FCFB9-5608-4850-A5ED-A67330838BBD}"/>
+    <hyperlink ref="I33" r:id="rId93" xr:uid="{24847E9B-EC3B-4706-B5D7-E96299D8FCE7}"/>
+    <hyperlink ref="I35" r:id="rId94" xr:uid="{5D875E55-FA05-42F5-9624-D365B9FCF580}"/>
+    <hyperlink ref="I36" r:id="rId95" xr:uid="{BC52199B-D637-4949-B7E2-EE16E5CCF544}"/>
+    <hyperlink ref="I37" r:id="rId96" xr:uid="{E285E0E1-E10F-4573-8B5D-14393F2018FF}"/>
+    <hyperlink ref="I38" r:id="rId97" xr:uid="{3E7CA2F9-EE2D-43F1-9F9C-30E7DB42ECF5}"/>
+    <hyperlink ref="I39" r:id="rId98" xr:uid="{928AC6DA-16BB-4AF8-8DB1-9ED23834C460}"/>
+    <hyperlink ref="I40" r:id="rId99" xr:uid="{E536F454-463E-4283-B208-0F490A944082}"/>
+    <hyperlink ref="I41" r:id="rId100" xr:uid="{850B09B6-55C1-4798-906D-B273A1D81D5C}"/>
+    <hyperlink ref="I42" r:id="rId101" xr:uid="{3CB74BBF-4D3F-4BC1-96C4-ADF57D2DE694}"/>
+    <hyperlink ref="I43" r:id="rId102" xr:uid="{12FE35A1-E3EB-4149-A6AF-D5686FDB1D00}"/>
+    <hyperlink ref="I44" r:id="rId103" xr:uid="{E1D776BB-59E6-4EDD-9DE7-DF885C654024}"/>
+    <hyperlink ref="I45" r:id="rId104" xr:uid="{3FCCCC27-14FE-489A-BA41-BE93FAB29F18}"/>
+    <hyperlink ref="I46" r:id="rId105" xr:uid="{E1A118C9-2C49-485A-8CFD-68FA8DF10434}"/>
+    <hyperlink ref="I47" r:id="rId106" xr:uid="{6BA16956-09AD-4E19-A6B3-3865374CA990}"/>
+    <hyperlink ref="I49" r:id="rId107" xr:uid="{83BE5218-6875-49A8-956E-1D08C7D5D1FA}"/>
+    <hyperlink ref="I50" r:id="rId108" xr:uid="{79738EA3-AAF9-4607-9485-79FB032A5B93}"/>
+    <hyperlink ref="I51" r:id="rId109" xr:uid="{16B23793-DE5C-40D5-8508-81CB751A116B}"/>
+    <hyperlink ref="I52" r:id="rId110" xr:uid="{B45AC07C-6967-40DF-AA68-11D16638538C}"/>
+    <hyperlink ref="I53" r:id="rId111" xr:uid="{029EB02F-755A-41DD-8B1B-9F81260CB5B3}"/>
+    <hyperlink ref="I54" r:id="rId112" xr:uid="{EEFDDD39-4424-4F94-88FF-8697250AA9D7}"/>
+    <hyperlink ref="I5" r:id="rId113" xr:uid="{F8E4F2FF-1D44-4D69-9803-4650A607B7B2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4525,16 +4525,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>240</v>
+        <v>187</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>242</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -4546,13 +4546,13 @@
         <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -4565,16 +4565,16 @@
         <v>IP-002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F3" s="2">
         <v>4</v>
@@ -4586,16 +4586,16 @@
         <v>IP-003</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F4" s="2">
         <v>10</v>
@@ -4607,16 +4607,16 @@
         <v>IP-005</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F5" s="2">
         <v>24</v>
@@ -4628,16 +4628,16 @@
         <v>IP-008</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -4649,16 +4649,16 @@
         <v>IP-009</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F7" s="2">
         <v>7</v>
@@ -4670,16 +4670,16 @@
         <v>IP-010</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F8" s="2">
         <v>3</v>
@@ -4691,16 +4691,16 @@
         <v>IP-011</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -4712,16 +4712,16 @@
         <v>IP-013</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F10" s="2">
         <v>8</v>
@@ -4733,16 +4733,16 @@
         <v>IP-014</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F11" s="2">
         <v>2</v>
@@ -4754,16 +4754,16 @@
         <v>IP-015</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
@@ -4775,16 +4775,16 @@
         <v>IP-016</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F13" s="2">
         <v>16</v>
@@ -4796,16 +4796,16 @@
         <v>IP-019</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F14" s="2">
         <v>10</v>
@@ -4817,16 +4817,16 @@
         <v>Not Found</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -4838,16 +4838,16 @@
         <v>Not Found</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -4859,16 +4859,16 @@
         <v>IP-023</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
@@ -4880,16 +4880,16 @@
         <v>IP-024</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
@@ -4901,16 +4901,16 @@
         <v>IP-025</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -4922,16 +4922,16 @@
         <v>IP-030</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F20" s="2">
         <v>5</v>
@@ -4943,16 +4943,16 @@
         <v>IP-031</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F21" s="2">
         <v>8</v>
@@ -4964,16 +4964,16 @@
         <v>Not Found</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F22" s="2">
         <v>12</v>
@@ -4985,16 +4985,16 @@
         <v>IP-033</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F23" s="2">
         <v>1</v>
@@ -5006,16 +5006,16 @@
         <v>Not Found</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F24" s="2">
         <v>1</v>
@@ -5027,16 +5027,16 @@
         <v>IP-035</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F25" s="2">
         <v>2</v>
@@ -5048,16 +5048,16 @@
         <v>IP-047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F26" s="2">
         <v>9</v>
@@ -5069,16 +5069,16 @@
         <v>IP-031</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F27" s="2">
         <v>26</v>
@@ -5090,16 +5090,16 @@
         <v>IP-005</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="F28" s="2">
         <v>15</v>
@@ -5111,16 +5111,16 @@
         <v>IP-005</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="F29" s="2">
         <v>14</v>
@@ -5132,16 +5132,16 @@
         <v>IP-009</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="F30" s="2">
         <v>2</v>
@@ -5153,16 +5153,16 @@
         <v>IP-016</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="F31" s="2">
         <v>4</v>
@@ -5174,16 +5174,16 @@
         <v>IP-047</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -5195,16 +5195,16 @@
         <v>IP-010</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="F33" s="2">
         <v>2</v>
@@ -5216,16 +5216,16 @@
         <v>IP-005</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="F34" s="2">
         <v>2</v>
@@ -5237,16 +5237,16 @@
         <v>IP-020</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="F35" s="2">
         <v>4</v>
@@ -5258,16 +5258,16 @@
         <v>IP-010</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="F36" s="2">
         <v>2</v>
@@ -5279,16 +5279,16 @@
         <v>IP-016</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="F37" s="2">
         <v>4</v>
@@ -5300,16 +5300,16 @@
         <v>IP-031</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="F38" s="2">
         <v>4</v>
@@ -5321,16 +5321,16 @@
         <v>IP-036</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="F39" s="2">
         <v>1</v>
@@ -5342,16 +5342,16 @@
         <v>IP-004</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
@@ -5363,16 +5363,16 @@
         <v>IP-005</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="F41" s="2">
         <v>2</v>
@@ -5384,16 +5384,16 @@
         <v>IP-005</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>261</v>
+        <v>208</v>
       </c>
       <c r="F42" s="2">
         <v>6</v>
@@ -5405,16 +5405,16 @@
         <v>IP-014</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>263</v>
+        <v>210</v>
       </c>
       <c r="F43" s="2">
         <v>1</v>
@@ -5426,16 +5426,16 @@
         <v>IP-020</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>263</v>
+        <v>210</v>
       </c>
       <c r="F44" s="2">
         <v>3</v>
@@ -5447,16 +5447,16 @@
         <v>IP-009</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>263</v>
+        <v>210</v>
       </c>
       <c r="F45" s="2">
         <v>2</v>
@@ -5468,16 +5468,16 @@
         <v>IP-031</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>263</v>
+        <v>210</v>
       </c>
       <c r="F46" s="2">
         <v>4</v>
@@ -5489,16 +5489,16 @@
         <v>IP-005</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>263</v>
+        <v>210</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -5510,16 +5510,16 @@
         <v>IP-019</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>263</v>
+        <v>210</v>
       </c>
       <c r="F48" s="2">
         <v>1</v>
@@ -5531,16 +5531,16 @@
         <v>IP-003</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>263</v>
+        <v>210</v>
       </c>
       <c r="F49" s="2">
         <v>2</v>
@@ -5552,16 +5552,16 @@
         <v>IP-005</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>265</v>
+        <v>212</v>
       </c>
       <c r="F50" s="2">
         <v>6</v>
@@ -5573,16 +5573,16 @@
         <v>IP-031</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>266</v>
+        <v>213</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>267</v>
+        <v>214</v>
       </c>
       <c r="F51" s="2">
         <v>20</v>
@@ -5594,16 +5594,16 @@
         <v>IP-016</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>266</v>
+        <v>213</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>267</v>
+        <v>214</v>
       </c>
       <c r="F52" s="2">
         <v>10</v>
@@ -5615,16 +5615,16 @@
         <v>IP-013</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>266</v>
+        <v>213</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>267</v>
+        <v>214</v>
       </c>
       <c r="F53" s="2">
         <v>1</v>
@@ -5636,16 +5636,16 @@
         <v>IP-047</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>266</v>
+        <v>213</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>267</v>
+        <v>214</v>
       </c>
       <c r="F54" s="2">
         <v>1</v>
@@ -5657,16 +5657,16 @@
         <v>IP-005</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>266</v>
+        <v>213</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>267</v>
+        <v>214</v>
       </c>
       <c r="F55" s="2">
         <v>10</v>
@@ -5678,16 +5678,16 @@
         <v>IP-020</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>266</v>
+        <v>213</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>267</v>
+        <v>214</v>
       </c>
       <c r="F56" s="2">
         <v>5</v>
@@ -5699,16 +5699,16 @@
         <v>IP-019</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>266</v>
+        <v>213</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>267</v>
+        <v>214</v>
       </c>
       <c r="F57" s="2">
         <v>3</v>
@@ -5720,16 +5720,16 @@
         <v>IP-005</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="F58" s="2">
         <v>8</v>
@@ -5741,16 +5741,16 @@
         <v>IP-020</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="F59" s="2">
         <v>4</v>
@@ -5762,16 +5762,16 @@
         <v>IP-019</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="F60" s="2">
         <v>6</v>
@@ -5783,16 +5783,16 @@
         <v>IP-014</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="F61" s="2">
         <v>1</v>
@@ -5804,16 +5804,16 @@
         <v>IP-040</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="F62" s="2">
         <v>1</v>
@@ -5825,16 +5825,16 @@
         <v>IP-010</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="F63" s="2">
         <v>2</v>
@@ -5846,16 +5846,16 @@
         <v>IP-019</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="F64" s="2">
         <v>2</v>
@@ -5867,16 +5867,16 @@
         <v>IP-031</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="F65" s="2">
         <v>6</v>
@@ -5888,16 +5888,16 @@
         <v>IP-014</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="F66" s="2">
         <v>1</v>
@@ -5909,16 +5909,16 @@
         <v>IP-005</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="F67" s="2">
         <v>4</v>
@@ -5930,16 +5930,16 @@
         <v>IP-014</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="F68" s="2">
         <v>1</v>
@@ -5951,16 +5951,16 @@
         <v>IP-019</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="F69" s="2">
         <v>2</v>
@@ -5972,16 +5972,16 @@
         <v>IP-031</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="F70" s="2">
         <v>20</v>
@@ -5993,16 +5993,16 @@
         <v>IP-016</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="F71" s="2">
         <v>10</v>
@@ -6014,16 +6014,16 @@
         <v>IP-036</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>265</v>
+        <v>212</v>
       </c>
       <c r="F72" s="2">
         <v>1</v>
@@ -6035,16 +6035,16 @@
         <v>IP-019</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>265</v>
+        <v>212</v>
       </c>
       <c r="F73" s="2">
         <v>10</v>
@@ -6056,16 +6056,16 @@
         <v>IP-031</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>265</v>
+        <v>212</v>
       </c>
       <c r="F74" s="2">
         <v>2</v>
@@ -6077,16 +6077,16 @@
         <v>IP-020</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>265</v>
+        <v>212</v>
       </c>
       <c r="F75" s="2">
         <v>2</v>
@@ -6098,16 +6098,16 @@
         <v>IP-014</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>265</v>
+        <v>212</v>
       </c>
       <c r="F76" s="2">
         <v>1</v>
@@ -6119,16 +6119,16 @@
         <v>IP-020</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F77" s="2">
         <v>7</v>
@@ -6140,16 +6140,16 @@
         <v>IP-014</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F78" s="2">
         <v>2</v>
@@ -6161,16 +6161,16 @@
         <v>IP-016</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F79" s="2">
         <v>1</v>
@@ -6182,16 +6182,16 @@
         <v>IP-045</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F80" s="2">
         <v>1</v>
@@ -6203,16 +6203,16 @@
         <v>IP-007</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F81" s="2">
         <v>1</v>
@@ -6224,16 +6224,16 @@
         <v>IP-019</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F82" s="2">
         <v>3</v>
@@ -6245,16 +6245,16 @@
         <v>IP-010</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F83" s="2">
         <v>1</v>
@@ -6266,16 +6266,16 @@
         <v>IP-009</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F84" s="2">
         <v>2</v>
@@ -6287,16 +6287,16 @@
         <v>IP-007</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F85" s="2">
         <v>1</v>
@@ -6308,16 +6308,16 @@
         <v>IP-036</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F86" s="2">
         <v>1</v>
@@ -6329,16 +6329,16 @@
         <v>IP-035</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F87" s="2">
         <v>2</v>
@@ -6350,16 +6350,16 @@
         <v>IP-036</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F88" s="2">
         <v>1</v>
@@ -6371,16 +6371,16 @@
         <v>IP-005</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F89" s="2">
         <v>4</v>
@@ -6392,16 +6392,16 @@
         <v>IP-002</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="F90" s="2">
         <v>1</v>
@@ -6413,16 +6413,16 @@
         <v>IP-019</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>274</v>
+        <v>221</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>275</v>
+        <v>222</v>
       </c>
       <c r="F91" s="2">
         <v>2</v>
@@ -6434,16 +6434,16 @@
         <v>IP-039</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>274</v>
+        <v>221</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>275</v>
+        <v>222</v>
       </c>
       <c r="F92" s="2">
         <v>2</v>
@@ -6455,16 +6455,16 @@
         <v>IP-005</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>274</v>
+        <v>221</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>275</v>
+        <v>222</v>
       </c>
       <c r="F93" s="2">
         <v>2</v>
@@ -6476,16 +6476,16 @@
         <v>IP-046</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>274</v>
+        <v>221</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>275</v>
+        <v>222</v>
       </c>
       <c r="F94" s="2">
         <v>1</v>
@@ -6497,16 +6497,16 @@
         <v>IP-040</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>274</v>
+        <v>221</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>275</v>
+        <v>222</v>
       </c>
       <c r="F95" s="2">
         <v>1</v>
@@ -6518,16 +6518,16 @@
         <v>IP-036</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>274</v>
+        <v>221</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>275</v>
+        <v>222</v>
       </c>
       <c r="F96" s="2">
         <v>1</v>
@@ -6539,16 +6539,16 @@
         <v>IP-019</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>276</v>
+        <v>223</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="F97" s="2">
         <v>5</v>
@@ -6560,16 +6560,16 @@
         <v>IP-039</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F98" s="2">
         <v>1</v>
@@ -6581,16 +6581,16 @@
         <v>IP-041</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F99" s="2">
         <v>1</v>
@@ -6602,16 +6602,16 @@
         <v>IP-040</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F100" s="2">
         <v>2</v>
@@ -6623,16 +6623,16 @@
         <v>IP-037</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F101" s="2">
         <v>1</v>
@@ -6644,16 +6644,16 @@
         <v>IP-020</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F102" s="2">
         <v>1</v>
@@ -6665,16 +6665,16 @@
         <v>IP-018</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F103" s="2">
         <v>1</v>
@@ -6686,16 +6686,16 @@
         <v>IP-019</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F104" s="2">
         <v>1</v>
@@ -6707,16 +6707,16 @@
         <v>Not Found</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>232</v>
+        <v>181</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F105" s="2">
         <v>1</v>
@@ -6728,16 +6728,16 @@
         <v>IP-043</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F106" s="2">
         <v>1</v>
@@ -6749,16 +6749,16 @@
         <v>IP-036</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F107" s="2">
         <v>3</v>
@@ -6770,16 +6770,16 @@
         <v>IP-002</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F108" s="2">
         <v>1</v>
@@ -6791,16 +6791,16 @@
         <v>IP-039</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="F109" s="2">
         <v>1</v>
@@ -6812,16 +6812,16 @@
         <v>IP-045</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="F110" s="2">
         <v>9</v>
@@ -6833,16 +6833,16 @@
         <v>IP-014</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F111" s="2">
         <v>6</v>
@@ -6854,16 +6854,16 @@
         <v>IP-043</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F112" s="2">
         <v>10</v>
@@ -6875,16 +6875,16 @@
         <v>IP-020</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F113" s="2">
         <v>6</v>
@@ -6896,16 +6896,16 @@
         <v>IP-041</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F114" s="2">
         <v>2</v>
@@ -6917,16 +6917,16 @@
         <v>IP-031</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F115" s="2">
         <v>5</v>
@@ -6938,16 +6938,16 @@
         <v>IP-005</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F116" s="2">
         <v>3</v>
@@ -6959,16 +6959,16 @@
         <v>IP-042</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F117" s="2">
         <v>1</v>
@@ -6980,16 +6980,16 @@
         <v>IP-037</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F118" s="2">
         <v>1</v>
@@ -7001,16 +7001,16 @@
         <v>IP-038</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F119" s="2">
         <v>8</v>
@@ -7022,16 +7022,16 @@
         <v>IP-019</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F120" s="2">
         <v>1</v>
@@ -7043,16 +7043,16 @@
         <v>IP-017</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F121" s="2">
         <v>2</v>
@@ -7064,16 +7064,16 @@
         <v>IP-035</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F122" s="2">
         <v>1</v>
@@ -7085,16 +7085,16 @@
         <v>Not Found</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F123" s="2">
         <v>1</v>
@@ -7106,16 +7106,16 @@
         <v>IP-036</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F124" s="2">
         <v>6</v>
@@ -7127,16 +7127,16 @@
         <v>IP-033</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F125" s="2">
         <v>1</v>
@@ -7148,16 +7148,16 @@
         <v>IP-039</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F126" s="2">
         <v>1</v>
@@ -7169,16 +7169,16 @@
         <v>IP-012</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F127" s="2">
         <v>1</v>
@@ -7190,16 +7190,16 @@
         <v>IP-009</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F128" s="2">
         <v>5</v>
@@ -7211,16 +7211,16 @@
         <v>IP-006</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F129" s="2">
         <v>2</v>
@@ -7232,16 +7232,16 @@
         <v>IP-003</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="F130" s="2">
         <v>2</v>
@@ -7253,16 +7253,16 @@
         <v>IP-015</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="F131" s="2">
         <v>4</v>
@@ -7274,16 +7274,16 @@
         <v>IP-014</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="F132" s="2">
         <v>19</v>
@@ -7295,16 +7295,16 @@
         <v>IP-039</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="F133" s="2">
         <v>1</v>
@@ -7316,16 +7316,16 @@
         <v>IP-044</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="F134" s="2">
         <v>10</v>
@@ -7337,16 +7337,16 @@
         <v>IP-036</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="F135" s="2">
         <v>3</v>
@@ -7358,16 +7358,16 @@
         <v>IP-048</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="F136" s="2">
         <v>1</v>
@@ -7379,16 +7379,16 @@
         <v>IP-009</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="F137" s="2">
         <v>2</v>
@@ -7400,16 +7400,16 @@
         <v>IP-012</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>282</v>
+        <v>229</v>
       </c>
       <c r="F138" s="2">
         <v>1</v>
@@ -7421,16 +7421,16 @@
         <v>IP-049</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>220</v>
+        <v>172</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>282</v>
+        <v>229</v>
       </c>
       <c r="F139" s="2">
         <v>1</v>
@@ -7442,16 +7442,16 @@
         <v>IP-050</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>283</v>
+        <v>230</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>282</v>
+        <v>229</v>
       </c>
       <c r="F140" s="2">
         <v>2</v>
@@ -7463,16 +7463,16 @@
         <v>IP-051</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>282</v>
+        <v>229</v>
       </c>
       <c r="F141" s="2">
         <v>2</v>
@@ -7484,16 +7484,16 @@
         <v>Not Found</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>282</v>
+        <v>229</v>
       </c>
       <c r="F142" s="2">
         <v>1</v>
@@ -7505,16 +7505,16 @@
         <v>IP-029</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>282</v>
+        <v>229</v>
       </c>
       <c r="F143" s="2">
         <v>1</v>
@@ -7526,16 +7526,16 @@
         <v>Not Found</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>282</v>
+        <v>229</v>
       </c>
       <c r="F144" s="2">
         <v>1</v>
@@ -7547,16 +7547,16 @@
         <v>IP-028</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>282</v>
+        <v>229</v>
       </c>
       <c r="F145" s="2">
         <v>1</v>
@@ -7568,16 +7568,16 @@
         <v>Not Found</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>232</v>
+        <v>181</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="F146" s="2">
         <v>1</v>
@@ -7589,16 +7589,16 @@
         <v>IP-005</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E147" s="25" t="s">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="F147" s="2">
         <v>7</v>
@@ -7610,16 +7610,16 @@
         <v>IP-020</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E148" s="25" t="s">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="F148" s="2">
         <v>6</v>
@@ -7631,16 +7631,16 @@
         <v>IP-048</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E149" s="25" t="s">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="F149" s="2">
         <v>8</v>
@@ -7652,16 +7652,16 @@
         <v>IP-013</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E150" s="25" t="s">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="F150" s="2">
         <v>2</v>
@@ -7673,16 +7673,16 @@
         <v>Not Found</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E151" s="25" t="s">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="F151" s="2">
         <v>2</v>
@@ -7694,16 +7694,16 @@
         <v>IP-014</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E152" s="25" t="s">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="F152" s="2">
         <v>1</v>
@@ -7715,16 +7715,16 @@
         <v>IP-015</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E153" s="25" t="s">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="F153" s="2">
         <v>3</v>
@@ -7736,16 +7736,16 @@
         <v>IP-044</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E154" s="25" t="s">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="F154" s="2">
         <v>1</v>
@@ -7757,16 +7757,16 @@
         <v>IP-053</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E155" s="26" t="s">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="F155" s="2">
         <v>1</v>
@@ -7778,16 +7778,16 @@
         <v>IP-043</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="F156" s="2">
         <v>1</v>
@@ -7799,16 +7799,16 @@
         <v>IP-013</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="F157" s="2">
         <v>1</v>
@@ -7820,16 +7820,16 @@
         <v>IP-019</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="F158" s="2">
         <v>2</v>
@@ -7841,16 +7841,16 @@
         <v>IP-019</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>265</v>
+        <v>212</v>
       </c>
       <c r="F159" s="2">
         <v>5</v>
@@ -7862,16 +7862,16 @@
         <v>IP-008</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="F160" s="2">
         <v>1</v>
@@ -7883,16 +7883,16 @@
         <v>IP-047</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="F161" s="2">
         <v>2</v>
@@ -7904,16 +7904,16 @@
         <v>Not Found</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="F162" s="2">
         <v>1</v>
@@ -7925,16 +7925,16 @@
         <v>IP-015</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="F163" s="2">
         <v>1</v>
@@ -7946,16 +7946,16 @@
         <v>IP-005</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>265</v>
+        <v>212</v>
       </c>
       <c r="F164" s="2">
         <v>1</v>
